--- a/Reporte_Empaque_Pedido_vs_Entregado.xlsx
+++ b/Reporte_Empaque_Pedido_vs_Entregado.xlsx
@@ -79,13 +79,13 @@
     </font>
     <font>
       <name val="Segoe UI"/>
-      <color rgb="001E293B"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="0015803D"/>
+      <color rgb="001E293B"/>
       <sz val="9.5"/>
     </font>
     <font>
@@ -248,7 +248,7 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -266,13 +266,13 @@
     <xf numFmtId="3" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -300,7 +300,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -680,7 +680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -702,7 +702,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Órdenes 3354 en adelante con fecha de pedido asignada · 74 agrupaciones (337 órdenes de producción) · Generado el 21/09/2026 11:30</t>
+          <t>Órdenes 3354 en adelante con fecha de pedido asignada · 95 agrupaciones (392 órdenes de producción) · Generado el 30/09/2026 14:46</t>
         </is>
       </c>
     </row>
@@ -730,16 +730,16 @@
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="n">
-        <v>4007</v>
+        <v>4697</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1859</v>
+        <v>2451</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2148</v>
+        <v>2246</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.4639381083104567</v>
+        <v>0.5218224398552267</v>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
@@ -799,7 +799,7 @@
         <v>48</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="F8" s="13">
         <f>D8-E8</f>
@@ -830,13 +830,13 @@
         <v>72</v>
       </c>
       <c r="E9" s="20" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F9" s="19">
         <f>D9-E9</f>
         <v/>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="21">
         <f>IF(D9&gt;0, E9/D9, 0)</f>
         <v/>
       </c>
@@ -860,14 +860,14 @@
       <c r="D10" s="13" t="n">
         <v>60</v>
       </c>
-      <c r="E10" s="21" t="n">
-        <v>0</v>
+      <c r="E10" s="14" t="n">
+        <v>22</v>
       </c>
       <c r="F10" s="13">
         <f>D10-E10</f>
         <v/>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="21">
         <f>IF(D10&gt;0, E10/D10, 0)</f>
         <v/>
       </c>
@@ -898,7 +898,7 @@
         <f>D11-E11</f>
         <v/>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="21">
         <f>IF(D11&gt;0, E11/D11, 0)</f>
         <v/>
       </c>
@@ -929,7 +929,7 @@
         <f>D12-E12</f>
         <v/>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="21">
         <f>IF(D12&gt;0, E12/D12, 0)</f>
         <v/>
       </c>
@@ -954,13 +954,13 @@
         <v>72</v>
       </c>
       <c r="E13" s="20" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="F13" s="19">
         <f>D13-E13</f>
         <v/>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="21">
         <f>IF(D13&gt;0, E13/D13, 0)</f>
         <v/>
       </c>
@@ -991,7 +991,7 @@
         <f>D14-E14</f>
         <v/>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="21">
         <f>IF(D14&gt;0, E14/D14, 0)</f>
         <v/>
       </c>
@@ -1022,7 +1022,7 @@
         <f>D15-E15</f>
         <v/>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="21">
         <f>IF(D15&gt;0, E15/D15, 0)</f>
         <v/>
       </c>
@@ -1053,7 +1053,7 @@
         <f>D16-E16</f>
         <v/>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="15">
         <f>IF(D16&gt;0, E16/D16, 0)</f>
         <v/>
       </c>
@@ -1078,7 +1078,7 @@
         <v>24</v>
       </c>
       <c r="E17" s="20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F17" s="19">
         <f>D17-E17</f>
@@ -1115,7 +1115,7 @@
         <f>D18-E18</f>
         <v/>
       </c>
-      <c r="G18" s="15">
+      <c r="G18" s="21">
         <f>IF(D18&gt;0, E18/D18, 0)</f>
         <v/>
       </c>
@@ -1146,7 +1146,7 @@
         <f>D19-E19</f>
         <v/>
       </c>
-      <c r="G19" s="15">
+      <c r="G19" s="21">
         <f>IF(D19&gt;0, E19/D19, 0)</f>
         <v/>
       </c>
@@ -1177,7 +1177,7 @@
         <f>D20-E20</f>
         <v/>
       </c>
-      <c r="G20" s="15">
+      <c r="G20" s="21">
         <f>IF(D20&gt;0, E20/D20, 0)</f>
         <v/>
       </c>
@@ -1208,7 +1208,7 @@
         <f>D21-E21</f>
         <v/>
       </c>
-      <c r="G21" s="15">
+      <c r="G21" s="21">
         <f>IF(D21&gt;0, E21/D21, 0)</f>
         <v/>
       </c>
@@ -1239,7 +1239,7 @@
         <f>D22-E22</f>
         <v/>
       </c>
-      <c r="G22" s="15">
+      <c r="G22" s="21">
         <f>IF(D22&gt;0, E22/D22, 0)</f>
         <v/>
       </c>
@@ -1270,7 +1270,7 @@
         <f>D23-E23</f>
         <v/>
       </c>
-      <c r="G23" s="15">
+      <c r="G23" s="21">
         <f>IF(D23&gt;0, E23/D23, 0)</f>
         <v/>
       </c>
@@ -1295,13 +1295,13 @@
         <v>60</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F24" s="13">
         <f>D24-E24</f>
         <v/>
       </c>
-      <c r="G24" s="15">
+      <c r="G24" s="21">
         <f>IF(D24&gt;0, E24/D24, 0)</f>
         <v/>
       </c>
@@ -1326,13 +1326,13 @@
         <v>72</v>
       </c>
       <c r="E25" s="20" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F25" s="19">
         <f>D25-E25</f>
         <v/>
       </c>
-      <c r="G25" s="15">
+      <c r="G25" s="21">
         <f>IF(D25&gt;0, E25/D25, 0)</f>
         <v/>
       </c>
@@ -1357,13 +1357,13 @@
         <v>60</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F26" s="13">
         <f>D26-E26</f>
         <v/>
       </c>
-      <c r="G26" s="15">
+      <c r="G26" s="21">
         <f>IF(D26&gt;0, E26/D26, 0)</f>
         <v/>
       </c>
@@ -1394,7 +1394,7 @@
         <f>D27-E27</f>
         <v/>
       </c>
-      <c r="G27" s="22">
+      <c r="G27" s="15">
         <f>IF(D27&gt;0, E27/D27, 0)</f>
         <v/>
       </c>
@@ -1425,7 +1425,7 @@
         <f>D28-E28</f>
         <v/>
       </c>
-      <c r="G28" s="22">
+      <c r="G28" s="15">
         <f>IF(D28&gt;0, E28/D28, 0)</f>
         <v/>
       </c>
@@ -1456,7 +1456,7 @@
         <f>D29-E29</f>
         <v/>
       </c>
-      <c r="G29" s="15">
+      <c r="G29" s="21">
         <f>IF(D29&gt;0, E29/D29, 0)</f>
         <v/>
       </c>
@@ -1487,7 +1487,7 @@
         <f>D30-E30</f>
         <v/>
       </c>
-      <c r="G30" s="15">
+      <c r="G30" s="21">
         <f>IF(D30&gt;0, E30/D30, 0)</f>
         <v/>
       </c>
@@ -1518,7 +1518,7 @@
         <f>D31-E31</f>
         <v/>
       </c>
-      <c r="G31" s="15">
+      <c r="G31" s="21">
         <f>IF(D31&gt;0, E31/D31, 0)</f>
         <v/>
       </c>
@@ -1543,7 +1543,7 @@
         <v>48</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F32" s="13">
         <f>D32-E32</f>
@@ -1574,13 +1574,13 @@
         <v>60</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F33" s="19">
         <f>D33-E33</f>
         <v/>
       </c>
-      <c r="G33" s="15">
+      <c r="G33" s="21">
         <f>IF(D33&gt;0, E33/D33, 0)</f>
         <v/>
       </c>
@@ -1605,13 +1605,13 @@
         <v>72</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F34" s="13">
         <f>D34-E34</f>
         <v/>
       </c>
-      <c r="G34" s="15">
+      <c r="G34" s="21">
         <f>IF(D34&gt;0, E34/D34, 0)</f>
         <v/>
       </c>
@@ -1642,7 +1642,7 @@
         <f>D35-E35</f>
         <v/>
       </c>
-      <c r="G35" s="15">
+      <c r="G35" s="21">
         <f>IF(D35&gt;0, E35/D35, 0)</f>
         <v/>
       </c>
@@ -1673,7 +1673,7 @@
         <f>D36-E36</f>
         <v/>
       </c>
-      <c r="G36" s="22">
+      <c r="G36" s="15">
         <f>IF(D36&gt;0, E36/D36, 0)</f>
         <v/>
       </c>
@@ -1704,7 +1704,7 @@
         <f>D37-E37</f>
         <v/>
       </c>
-      <c r="G37" s="22">
+      <c r="G37" s="15">
         <f>IF(D37&gt;0, E37/D37, 0)</f>
         <v/>
       </c>
@@ -1729,13 +1729,13 @@
         <v>24</v>
       </c>
       <c r="E38" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F38" s="13">
         <f>D38-E38</f>
         <v/>
       </c>
-      <c r="G38" s="15">
+      <c r="G38" s="21">
         <f>IF(D38&gt;0, E38/D38, 0)</f>
         <v/>
       </c>
@@ -1766,7 +1766,7 @@
         <f>D39-E39</f>
         <v/>
       </c>
-      <c r="G39" s="22">
+      <c r="G39" s="15">
         <f>IF(D39&gt;0, E39/D39, 0)</f>
         <v/>
       </c>
@@ -1790,14 +1790,14 @@
       <c r="D40" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="E40" s="21" t="n">
+      <c r="E40" s="22" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="13">
         <f>D40-E40</f>
         <v/>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="21">
         <f>IF(D40&gt;0, E40/D40, 0)</f>
         <v/>
       </c>
@@ -1828,7 +1828,7 @@
         <f>D41-E41</f>
         <v/>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="21">
         <f>IF(D41&gt;0, E41/D41, 0)</f>
         <v/>
       </c>
@@ -1852,14 +1852,14 @@
       <c r="D42" s="13" t="n">
         <v>72</v>
       </c>
-      <c r="E42" s="21" t="n">
+      <c r="E42" s="22" t="n">
         <v>0</v>
       </c>
       <c r="F42" s="13">
         <f>D42-E42</f>
         <v/>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="21">
         <f>IF(D42&gt;0, E42/D42, 0)</f>
         <v/>
       </c>
@@ -1890,7 +1890,7 @@
         <f>D43-E43</f>
         <v/>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="21">
         <f>IF(D43&gt;0, E43/D43, 0)</f>
         <v/>
       </c>
@@ -1914,14 +1914,14 @@
       <c r="D44" s="13" t="n">
         <v>60</v>
       </c>
-      <c r="E44" s="21" t="n">
+      <c r="E44" s="22" t="n">
         <v>0</v>
       </c>
       <c r="F44" s="13">
         <f>D44-E44</f>
         <v/>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="21">
         <f>IF(D44&gt;0, E44/D44, 0)</f>
         <v/>
       </c>
@@ -1952,7 +1952,7 @@
         <f>D45-E45</f>
         <v/>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="21">
         <f>IF(D45&gt;0, E45/D45, 0)</f>
         <v/>
       </c>
@@ -1974,16 +1974,16 @@
         </is>
       </c>
       <c r="D46" s="13" t="n">
-        <v>24</v>
-      </c>
-      <c r="E46" s="21" t="n">
+        <v>48</v>
+      </c>
+      <c r="E46" s="22" t="n">
         <v>0</v>
       </c>
       <c r="F46" s="13">
         <f>D46-E46</f>
         <v/>
       </c>
-      <c r="G46" s="15">
+      <c r="G46" s="21">
         <f>IF(D46&gt;0, E46/D46, 0)</f>
         <v/>
       </c>
@@ -2005,7 +2005,7 @@
         </is>
       </c>
       <c r="D47" s="19" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E47" s="23" t="n">
         <v>0</v>
@@ -2014,7 +2014,7 @@
         <f>D47-E47</f>
         <v/>
       </c>
-      <c r="G47" s="15">
+      <c r="G47" s="21">
         <f>IF(D47&gt;0, E47/D47, 0)</f>
         <v/>
       </c>
@@ -2038,14 +2038,14 @@
       <c r="D48" s="13" t="n">
         <v>72</v>
       </c>
-      <c r="E48" s="21" t="n">
+      <c r="E48" s="22" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="13">
         <f>D48-E48</f>
         <v/>
       </c>
-      <c r="G48" s="15">
+      <c r="G48" s="21">
         <f>IF(D48&gt;0, E48/D48, 0)</f>
         <v/>
       </c>
@@ -2076,7 +2076,7 @@
         <f>D49-E49</f>
         <v/>
       </c>
-      <c r="G49" s="15">
+      <c r="G49" s="21">
         <f>IF(D49&gt;0, E49/D49, 0)</f>
         <v/>
       </c>
@@ -2100,14 +2100,14 @@
       <c r="D50" s="13" t="n">
         <v>72</v>
       </c>
-      <c r="E50" s="21" t="n">
+      <c r="E50" s="22" t="n">
         <v>0</v>
       </c>
       <c r="F50" s="13">
         <f>D50-E50</f>
         <v/>
       </c>
-      <c r="G50" s="15">
+      <c r="G50" s="21">
         <f>IF(D50&gt;0, E50/D50, 0)</f>
         <v/>
       </c>
@@ -2138,7 +2138,7 @@
         <f>D51-E51</f>
         <v/>
       </c>
-      <c r="G51" s="15">
+      <c r="G51" s="21">
         <f>IF(D51&gt;0, E51/D51, 0)</f>
         <v/>
       </c>
@@ -2162,14 +2162,14 @@
       <c r="D52" s="13" t="n">
         <v>48</v>
       </c>
-      <c r="E52" s="21" t="n">
+      <c r="E52" s="22" t="n">
         <v>0</v>
       </c>
       <c r="F52" s="13">
         <f>D52-E52</f>
         <v/>
       </c>
-      <c r="G52" s="15">
+      <c r="G52" s="21">
         <f>IF(D52&gt;0, E52/D52, 0)</f>
         <v/>
       </c>
@@ -2200,7 +2200,7 @@
         <f>D53-E53</f>
         <v/>
       </c>
-      <c r="G53" s="15">
+      <c r="G53" s="21">
         <f>IF(D53&gt;0, E53/D53, 0)</f>
         <v/>
       </c>
@@ -2224,14 +2224,14 @@
       <c r="D54" s="13" t="n">
         <v>72</v>
       </c>
-      <c r="E54" s="21" t="n">
+      <c r="E54" s="22" t="n">
         <v>0</v>
       </c>
       <c r="F54" s="13">
         <f>D54-E54</f>
         <v/>
       </c>
-      <c r="G54" s="15">
+      <c r="G54" s="21">
         <f>IF(D54&gt;0, E54/D54, 0)</f>
         <v/>
       </c>
@@ -2256,13 +2256,13 @@
         <v>48</v>
       </c>
       <c r="E55" s="20" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F55" s="19">
         <f>D55-E55</f>
         <v/>
       </c>
-      <c r="G55" s="15">
+      <c r="G55" s="21">
         <f>IF(D55&gt;0, E55/D55, 0)</f>
         <v/>
       </c>
@@ -2287,13 +2287,13 @@
         <v>60</v>
       </c>
       <c r="E56" s="14" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F56" s="13">
         <f>D56-E56</f>
         <v/>
       </c>
-      <c r="G56" s="15">
+      <c r="G56" s="21">
         <f>IF(D56&gt;0, E56/D56, 0)</f>
         <v/>
       </c>
@@ -2324,7 +2324,7 @@
         <f>D57-E57</f>
         <v/>
       </c>
-      <c r="G57" s="22">
+      <c r="G57" s="15">
         <f>IF(D57&gt;0, E57/D57, 0)</f>
         <v/>
       </c>
@@ -2355,7 +2355,7 @@
         <f>D58-E58</f>
         <v/>
       </c>
-      <c r="G58" s="22">
+      <c r="G58" s="15">
         <f>IF(D58&gt;0, E58/D58, 0)</f>
         <v/>
       </c>
@@ -2380,13 +2380,13 @@
         <v>48</v>
       </c>
       <c r="E59" s="20" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F59" s="19">
         <f>D59-E59</f>
         <v/>
       </c>
-      <c r="G59" s="15">
+      <c r="G59" s="21">
         <f>IF(D59&gt;0, E59/D59, 0)</f>
         <v/>
       </c>
@@ -2411,13 +2411,13 @@
         <v>60</v>
       </c>
       <c r="E60" s="14" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F60" s="13">
         <f>D60-E60</f>
         <v/>
       </c>
-      <c r="G60" s="15">
+      <c r="G60" s="21">
         <f>IF(D60&gt;0, E60/D60, 0)</f>
         <v/>
       </c>
@@ -2442,13 +2442,13 @@
         <v>48</v>
       </c>
       <c r="E61" s="20" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F61" s="19">
         <f>D61-E61</f>
         <v/>
       </c>
-      <c r="G61" s="15">
+      <c r="G61" s="21">
         <f>IF(D61&gt;0, E61/D61, 0)</f>
         <v/>
       </c>
@@ -2473,13 +2473,13 @@
         <v>48</v>
       </c>
       <c r="E62" s="14" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="F62" s="13">
         <f>D62-E62</f>
         <v/>
       </c>
-      <c r="G62" s="15">
+      <c r="G62" s="21">
         <f>IF(D62&gt;0, E62/D62, 0)</f>
         <v/>
       </c>
@@ -2504,13 +2504,13 @@
         <v>72</v>
       </c>
       <c r="E63" s="20" t="n">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="F63" s="19">
         <f>D63-E63</f>
         <v/>
       </c>
-      <c r="G63" s="15">
+      <c r="G63" s="21">
         <f>IF(D63&gt;0, E63/D63, 0)</f>
         <v/>
       </c>
@@ -2535,13 +2535,13 @@
         <v>60</v>
       </c>
       <c r="E64" s="14" t="n">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="F64" s="13">
         <f>D64-E64</f>
         <v/>
       </c>
-      <c r="G64" s="15">
+      <c r="G64" s="21">
         <f>IF(D64&gt;0, E64/D64, 0)</f>
         <v/>
       </c>
@@ -2566,13 +2566,13 @@
         <v>48</v>
       </c>
       <c r="E65" s="20" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="F65" s="19">
         <f>D65-E65</f>
         <v/>
       </c>
-      <c r="G65" s="15">
+      <c r="G65" s="21">
         <f>IF(D65&gt;0, E65/D65, 0)</f>
         <v/>
       </c>
@@ -2596,14 +2596,14 @@
       <c r="D66" s="13" t="n">
         <v>60</v>
       </c>
-      <c r="E66" s="21" t="n">
-        <v>0</v>
+      <c r="E66" s="14" t="n">
+        <v>21</v>
       </c>
       <c r="F66" s="13">
         <f>D66-E66</f>
         <v/>
       </c>
-      <c r="G66" s="15">
+      <c r="G66" s="21">
         <f>IF(D66&gt;0, E66/D66, 0)</f>
         <v/>
       </c>
@@ -2627,14 +2627,14 @@
       <c r="D67" s="19" t="n">
         <v>48</v>
       </c>
-      <c r="E67" s="23" t="n">
-        <v>0</v>
+      <c r="E67" s="20" t="n">
+        <v>18</v>
       </c>
       <c r="F67" s="19">
         <f>D67-E67</f>
         <v/>
       </c>
-      <c r="G67" s="15">
+      <c r="G67" s="21">
         <f>IF(D67&gt;0, E67/D67, 0)</f>
         <v/>
       </c>
@@ -2658,14 +2658,14 @@
       <c r="D68" s="13" t="n">
         <v>60</v>
       </c>
-      <c r="E68" s="21" t="n">
-        <v>0</v>
+      <c r="E68" s="14" t="n">
+        <v>18</v>
       </c>
       <c r="F68" s="13">
         <f>D68-E68</f>
         <v/>
       </c>
-      <c r="G68" s="15">
+      <c r="G68" s="21">
         <f>IF(D68&gt;0, E68/D68, 0)</f>
         <v/>
       </c>
@@ -2689,14 +2689,14 @@
       <c r="D69" s="19" t="n">
         <v>60</v>
       </c>
-      <c r="E69" s="23" t="n">
-        <v>0</v>
+      <c r="E69" s="20" t="n">
+        <v>48</v>
       </c>
       <c r="F69" s="19">
         <f>D69-E69</f>
         <v/>
       </c>
-      <c r="G69" s="15">
+      <c r="G69" s="21">
         <f>IF(D69&gt;0, E69/D69, 0)</f>
         <v/>
       </c>
@@ -2720,14 +2720,14 @@
       <c r="D70" s="13" t="n">
         <v>60</v>
       </c>
-      <c r="E70" s="21" t="n">
-        <v>0</v>
+      <c r="E70" s="14" t="n">
+        <v>46</v>
       </c>
       <c r="F70" s="13">
         <f>D70-E70</f>
         <v/>
       </c>
-      <c r="G70" s="15">
+      <c r="G70" s="21">
         <f>IF(D70&gt;0, E70/D70, 0)</f>
         <v/>
       </c>
@@ -2752,13 +2752,13 @@
         <v>60</v>
       </c>
       <c r="E71" s="20" t="n">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F71" s="19">
         <f>D71-E71</f>
         <v/>
       </c>
-      <c r="G71" s="15">
+      <c r="G71" s="21">
         <f>IF(D71&gt;0, E71/D71, 0)</f>
         <v/>
       </c>
@@ -2782,14 +2782,14 @@
       <c r="D72" s="13" t="n">
         <v>48</v>
       </c>
-      <c r="E72" s="21" t="n">
-        <v>0</v>
+      <c r="E72" s="14" t="n">
+        <v>28</v>
       </c>
       <c r="F72" s="13">
         <f>D72-E72</f>
         <v/>
       </c>
-      <c r="G72" s="15">
+      <c r="G72" s="21">
         <f>IF(D72&gt;0, E72/D72, 0)</f>
         <v/>
       </c>
@@ -2813,14 +2813,14 @@
       <c r="D73" s="19" t="n">
         <v>48</v>
       </c>
-      <c r="E73" s="23" t="n">
-        <v>0</v>
+      <c r="E73" s="20" t="n">
+        <v>32</v>
       </c>
       <c r="F73" s="19">
         <f>D73-E73</f>
         <v/>
       </c>
-      <c r="G73" s="15">
+      <c r="G73" s="21">
         <f>IF(D73&gt;0, E73/D73, 0)</f>
         <v/>
       </c>
@@ -2844,14 +2844,14 @@
       <c r="D74" s="13" t="n">
         <v>48</v>
       </c>
-      <c r="E74" s="21" t="n">
-        <v>0</v>
+      <c r="E74" s="14" t="n">
+        <v>34</v>
       </c>
       <c r="F74" s="13">
         <f>D74-E74</f>
         <v/>
       </c>
-      <c r="G74" s="15">
+      <c r="G74" s="21">
         <f>IF(D74&gt;0, E74/D74, 0)</f>
         <v/>
       </c>
@@ -2876,13 +2876,13 @@
         <v>60</v>
       </c>
       <c r="E75" s="20" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="F75" s="19">
         <f>D75-E75</f>
         <v/>
       </c>
-      <c r="G75" s="15">
+      <c r="G75" s="21">
         <f>IF(D75&gt;0, E75/D75, 0)</f>
         <v/>
       </c>
@@ -2906,14 +2906,14 @@
       <c r="D76" s="13" t="n">
         <v>60</v>
       </c>
-      <c r="E76" s="21" t="n">
-        <v>0</v>
+      <c r="E76" s="14" t="n">
+        <v>48</v>
       </c>
       <c r="F76" s="13">
         <f>D76-E76</f>
         <v/>
       </c>
-      <c r="G76" s="15">
+      <c r="G76" s="21">
         <f>IF(D76&gt;0, E76/D76, 0)</f>
         <v/>
       </c>
@@ -2937,14 +2937,14 @@
       <c r="D77" s="19" t="n">
         <v>24</v>
       </c>
-      <c r="E77" s="23" t="n">
-        <v>0</v>
+      <c r="E77" s="20" t="n">
+        <v>12</v>
       </c>
       <c r="F77" s="19">
         <f>D77-E77</f>
         <v/>
       </c>
-      <c r="G77" s="15">
+      <c r="G77" s="21">
         <f>IF(D77&gt;0, E77/D77, 0)</f>
         <v/>
       </c>
@@ -2968,14 +2968,14 @@
       <c r="D78" s="13" t="n">
         <v>60</v>
       </c>
-      <c r="E78" s="21" t="n">
-        <v>0</v>
+      <c r="E78" s="14" t="n">
+        <v>11</v>
       </c>
       <c r="F78" s="13">
         <f>D78-E78</f>
         <v/>
       </c>
-      <c r="G78" s="15">
+      <c r="G78" s="21">
         <f>IF(D78&gt;0, E78/D78, 0)</f>
         <v/>
       </c>
@@ -3006,7 +3006,7 @@
         <f>D79-E79</f>
         <v/>
       </c>
-      <c r="G79" s="15">
+      <c r="G79" s="21">
         <f>IF(D79&gt;0, E79/D79, 0)</f>
         <v/>
       </c>
@@ -3030,14 +3030,14 @@
       <c r="D80" s="13" t="n">
         <v>60</v>
       </c>
-      <c r="E80" s="21" t="n">
+      <c r="E80" s="22" t="n">
         <v>0</v>
       </c>
       <c r="F80" s="13">
         <f>D80-E80</f>
         <v/>
       </c>
-      <c r="G80" s="15">
+      <c r="G80" s="21">
         <f>IF(D80&gt;0, E80/D80, 0)</f>
         <v/>
       </c>
@@ -3045,7 +3045,7 @@
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="16" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B81" s="17" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="C81" s="18" t="inlineStr">
         <is>
-          <t>VINO</t>
+          <t>BEIGE</t>
         </is>
       </c>
       <c r="D81" s="19" t="n">
@@ -3068,33 +3068,684 @@
         <f>D81-E81</f>
         <v/>
       </c>
-      <c r="G81" s="15">
+      <c r="G81" s="21">
         <f>IF(D81&gt;0, E81/D81, 0)</f>
         <v/>
       </c>
     </row>
-    <row r="82" ht="24" customHeight="1">
-      <c r="A82" s="24" t="inlineStr">
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t>MAFER</t>
+        </is>
+      </c>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>VINO</t>
+        </is>
+      </c>
+      <c r="D82" s="13" t="n">
+        <v>72</v>
+      </c>
+      <c r="E82" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="13">
+        <f>D82-E82</f>
+        <v/>
+      </c>
+      <c r="G82" s="21">
+        <f>IF(D82&gt;0, E82/D82, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="16" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="17" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="C83" s="18" t="inlineStr">
+        <is>
+          <t>CELESTE BB</t>
+        </is>
+      </c>
+      <c r="D83" s="19" t="n">
+        <v>48</v>
+      </c>
+      <c r="E83" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="19">
+        <f>D83-E83</f>
+        <v/>
+      </c>
+      <c r="G83" s="21">
+        <f>IF(D83&gt;0, E83/D83, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t>LILA</t>
+        </is>
+      </c>
+      <c r="D84" s="13" t="n">
+        <v>48</v>
+      </c>
+      <c r="E84" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="13">
+        <f>D84-E84</f>
+        <v/>
+      </c>
+      <c r="G84" s="21">
+        <f>IF(D84&gt;0, E84/D84, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="16" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="17" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="C85" s="18" t="inlineStr">
+        <is>
+          <t>MANTEQUILLA</t>
+        </is>
+      </c>
+      <c r="D85" s="19" t="n">
+        <v>48</v>
+      </c>
+      <c r="E85" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="19">
+        <f>D85-E85</f>
+        <v/>
+      </c>
+      <c r="G85" s="21">
+        <f>IF(D85&gt;0, E85/D85, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="11" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="C86" s="12" t="inlineStr">
+        <is>
+          <t>MELON</t>
+        </is>
+      </c>
+      <c r="D86" s="13" t="n">
+        <v>48</v>
+      </c>
+      <c r="E86" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="13">
+        <f>D86-E86</f>
+        <v/>
+      </c>
+      <c r="G86" s="21">
+        <f>IF(D86&gt;0, E86/D86, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="16" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="17" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="C87" s="18" t="inlineStr">
+        <is>
+          <t>ROSA</t>
+        </is>
+      </c>
+      <c r="D87" s="19" t="n">
+        <v>48</v>
+      </c>
+      <c r="E87" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="19">
+        <f>D87-E87</f>
+        <v/>
+      </c>
+      <c r="G87" s="21">
+        <f>IF(D87&gt;0, E87/D87, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="11" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>VINO</t>
+        </is>
+      </c>
+      <c r="D88" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="E88" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="13">
+        <f>D88-E88</f>
+        <v/>
+      </c>
+      <c r="G88" s="21">
+        <f>IF(D88&gt;0, E88/D88, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="16" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="17" t="inlineStr">
+        <is>
+          <t>CARLOTA</t>
+        </is>
+      </c>
+      <c r="C89" s="18" t="inlineStr">
+        <is>
+          <t>LEOPARDO</t>
+        </is>
+      </c>
+      <c r="D89" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="E89" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="19">
+        <f>D89-E89</f>
+        <v/>
+      </c>
+      <c r="G89" s="21">
+        <f>IF(D89&gt;0, E89/D89, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t>CRISTINA</t>
+        </is>
+      </c>
+      <c r="C90" s="12" t="inlineStr">
+        <is>
+          <t>PLATA QUEMADA</t>
+        </is>
+      </c>
+      <c r="D90" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E90" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="13">
+        <f>D90-E90</f>
+        <v/>
+      </c>
+      <c r="G90" s="21">
+        <f>IF(D90&gt;0, E90/D90, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="16" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="17" t="inlineStr">
+        <is>
+          <t>FABIANA</t>
+        </is>
+      </c>
+      <c r="C91" s="18" t="inlineStr">
+        <is>
+          <t>MORO</t>
+        </is>
+      </c>
+      <c r="D91" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="E91" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="19">
+        <f>D91-E91</f>
+        <v/>
+      </c>
+      <c r="G91" s="21">
+        <f>IF(D91&gt;0, E91/D91, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="10" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="11" t="inlineStr">
+        <is>
+          <t>GRETA</t>
+        </is>
+      </c>
+      <c r="C92" s="12" t="inlineStr">
+        <is>
+          <t>MARRON</t>
+        </is>
+      </c>
+      <c r="D92" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="E92" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="13">
+        <f>D92-E92</f>
+        <v/>
+      </c>
+      <c r="G92" s="21">
+        <f>IF(D92&gt;0, E92/D92, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="16" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="17" t="inlineStr">
+        <is>
+          <t>GRETA</t>
+        </is>
+      </c>
+      <c r="C93" s="18" t="inlineStr">
+        <is>
+          <t>VINO</t>
+        </is>
+      </c>
+      <c r="D93" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="E93" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="19">
+        <f>D93-E93</f>
+        <v/>
+      </c>
+      <c r="G93" s="21">
+        <f>IF(D93&gt;0, E93/D93, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="10" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
+          <t>MAFER</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="inlineStr">
+        <is>
+          <t>MARRON</t>
+        </is>
+      </c>
+      <c r="D94" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="E94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="13">
+        <f>D94-E94</f>
+        <v/>
+      </c>
+      <c r="G94" s="21">
+        <f>IF(D94&gt;0, E94/D94, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="16" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="17" t="inlineStr">
+        <is>
+          <t>MAFER</t>
+        </is>
+      </c>
+      <c r="C95" s="18" t="inlineStr">
+        <is>
+          <t>VINO</t>
+        </is>
+      </c>
+      <c r="D95" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="E95" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="19">
+        <f>D95-E95</f>
+        <v/>
+      </c>
+      <c r="G95" s="21">
+        <f>IF(D95&gt;0, E95/D95, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="10" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="11" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>CELESTE BB</t>
+        </is>
+      </c>
+      <c r="D96" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="E96" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="13">
+        <f>D96-E96</f>
+        <v/>
+      </c>
+      <c r="G96" s="21">
+        <f>IF(D96&gt;0, E96/D96, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="16" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="17" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="C97" s="18" t="inlineStr">
+        <is>
+          <t>LILA</t>
+        </is>
+      </c>
+      <c r="D97" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="E97" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="19">
+        <f>D97-E97</f>
+        <v/>
+      </c>
+      <c r="G97" s="21">
+        <f>IF(D97&gt;0, E97/D97, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="10" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="C98" s="12" t="inlineStr">
+        <is>
+          <t>MANTEQUILLA</t>
+        </is>
+      </c>
+      <c r="D98" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="E98" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="13">
+        <f>D98-E98</f>
+        <v/>
+      </c>
+      <c r="G98" s="21">
+        <f>IF(D98&gt;0, E98/D98, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="16" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="17" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="C99" s="18" t="inlineStr">
+        <is>
+          <t>MELON</t>
+        </is>
+      </c>
+      <c r="D99" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="E99" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="19">
+        <f>D99-E99</f>
+        <v/>
+      </c>
+      <c r="G99" s="21">
+        <f>IF(D99&gt;0, E99/D99, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="inlineStr">
+        <is>
+          <t>ROSA</t>
+        </is>
+      </c>
+      <c r="D100" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="E100" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="13">
+        <f>D100-E100</f>
+        <v/>
+      </c>
+      <c r="G100" s="21">
+        <f>IF(D100&gt;0, E100/D100, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="16" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="17" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="C101" s="18" t="inlineStr">
+        <is>
+          <t>VINO</t>
+        </is>
+      </c>
+      <c r="D101" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="E101" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="19">
+        <f>D101-E101</f>
+        <v/>
+      </c>
+      <c r="G101" s="21">
+        <f>IF(D101&gt;0, E101/D101, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t>DEMI</t>
+        </is>
+      </c>
+      <c r="C102" s="12" t="inlineStr">
+        <is>
+          <t>NEGRO</t>
+        </is>
+      </c>
+      <c r="D102" s="13" t="n">
+        <v>72</v>
+      </c>
+      <c r="E102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="13">
+        <f>D102-E102</f>
+        <v/>
+      </c>
+      <c r="G102" s="21">
+        <f>IF(D102&gt;0, E102/D102, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103" ht="24" customHeight="1">
+      <c r="A103" s="24" t="inlineStr">
         <is>
           <t>TOTAL GENERAL</t>
         </is>
       </c>
-      <c r="B82" s="25" t="inlineStr"/>
-      <c r="C82" s="25" t="inlineStr"/>
-      <c r="D82" s="26">
-        <f>SUM(D8:D81)</f>
-        <v/>
-      </c>
-      <c r="E82" s="26">
-        <f>SUM(E8:E81)</f>
-        <v/>
-      </c>
-      <c r="F82" s="27">
-        <f>D82-E82</f>
-        <v/>
-      </c>
-      <c r="G82" s="28">
-        <f>IF(D82&gt;0, E82/D82, 0)</f>
+      <c r="B103" s="25" t="inlineStr"/>
+      <c r="C103" s="25" t="inlineStr"/>
+      <c r="D103" s="26">
+        <f>SUM(D8:D102)</f>
+        <v/>
+      </c>
+      <c r="E103" s="26">
+        <f>SUM(E8:E102)</f>
+        <v/>
+      </c>
+      <c r="F103" s="27">
+        <f>D103-E103</f>
+        <v/>
+      </c>
+      <c r="G103" s="28">
+        <f>IF(D103&gt;0, E103/D103, 0)</f>
         <v/>
       </c>
     </row>
@@ -3113,7 +3764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I342"/>
+  <dimension ref="A1:I397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3137,7 +3788,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Detalle individual de cada orden con su estado en empaque · Total 337 órdenes</t>
+          <t>Detalle individual de cada orden con su estado en empaque · Total 392 órdenes</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3868,7 @@
         <f>E5-F5</f>
         <v/>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="21">
         <f>IF(E5&gt;0, F5/E5, 0)</f>
         <v/>
       </c>
@@ -3289,13 +3940,13 @@
         <v>12</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G7" s="13">
         <f>E7-F7</f>
         <v/>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="21">
         <f>IF(E7&gt;0, F7/E7, 0)</f>
         <v/>
       </c>
@@ -3328,7 +3979,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G8" s="19">
         <f>E8-F8</f>
@@ -3373,7 +4024,7 @@
         <f>E9-F9</f>
         <v/>
       </c>
-      <c r="H9" s="15">
+      <c r="H9" s="21">
         <f>IF(E9&gt;0, F9/E9, 0)</f>
         <v/>
       </c>
@@ -3445,13 +4096,13 @@
         <v>12</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G11" s="13">
         <f>E11-F11</f>
         <v/>
       </c>
-      <c r="H11" s="15">
+      <c r="H11" s="21">
         <f>IF(E11&gt;0, F11/E11, 0)</f>
         <v/>
       </c>
@@ -3523,13 +4174,13 @@
         <v>12</v>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G13" s="13">
         <f>E13-F13</f>
         <v/>
       </c>
-      <c r="H13" s="15">
+      <c r="H13" s="21">
         <f>IF(E13&gt;0, F13/E13, 0)</f>
         <v/>
       </c>
@@ -3562,7 +4213,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14" s="19">
         <f>E14-F14</f>
@@ -3601,13 +4252,13 @@
         <v>12</v>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G15" s="13">
         <f>E15-F15</f>
         <v/>
       </c>
-      <c r="H15" s="15">
+      <c r="H15" s="21">
         <f>IF(E15&gt;0, F15/E15, 0)</f>
         <v/>
       </c>
@@ -3640,7 +4291,7 @@
         <v>12</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G16" s="19">
         <f>E16-F16</f>
@@ -3679,13 +4330,13 @@
         <v>12</v>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G17" s="13">
         <f>E17-F17</f>
         <v/>
       </c>
-      <c r="H17" s="15">
+      <c r="H17" s="21">
         <f>IF(E17&gt;0, F17/E17, 0)</f>
         <v/>
       </c>
@@ -3718,7 +4369,7 @@
         <v>12</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="19">
         <f>E18-F18</f>
@@ -3757,13 +4408,13 @@
         <v>12</v>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G19" s="13">
         <f>E19-F19</f>
         <v/>
       </c>
-      <c r="H19" s="15">
+      <c r="H19" s="21">
         <f>IF(E19&gt;0, F19/E19, 0)</f>
         <v/>
       </c>
@@ -3841,7 +4492,7 @@
         <f>E21-F21</f>
         <v/>
       </c>
-      <c r="H21" s="15">
+      <c r="H21" s="21">
         <f>IF(E21&gt;0, F21/E21, 0)</f>
         <v/>
       </c>
@@ -3919,7 +4570,7 @@
         <f>E23-F23</f>
         <v/>
       </c>
-      <c r="H23" s="15">
+      <c r="H23" s="21">
         <f>IF(E23&gt;0, F23/E23, 0)</f>
         <v/>
       </c>
@@ -3997,7 +4648,7 @@
         <f>E25-F25</f>
         <v/>
       </c>
-      <c r="H25" s="15">
+      <c r="H25" s="21">
         <f>IF(E25&gt;0, F25/E25, 0)</f>
         <v/>
       </c>
@@ -4075,7 +4726,7 @@
         <f>E27-F27</f>
         <v/>
       </c>
-      <c r="H27" s="15">
+      <c r="H27" s="21">
         <f>IF(E27&gt;0, F27/E27, 0)</f>
         <v/>
       </c>
@@ -4153,7 +4804,7 @@
         <f>E29-F29</f>
         <v/>
       </c>
-      <c r="H29" s="15">
+      <c r="H29" s="21">
         <f>IF(E29&gt;0, F29/E29, 0)</f>
         <v/>
       </c>
@@ -4231,7 +4882,7 @@
         <f>E31-F31</f>
         <v/>
       </c>
-      <c r="H31" s="15">
+      <c r="H31" s="21">
         <f>IF(E31&gt;0, F31/E31, 0)</f>
         <v/>
       </c>
@@ -4303,13 +4954,13 @@
         <v>12</v>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G33" s="13">
         <f>E33-F33</f>
         <v/>
       </c>
-      <c r="H33" s="15">
+      <c r="H33" s="21">
         <f>IF(E33&gt;0, F33/E33, 0)</f>
         <v/>
       </c>
@@ -4387,7 +5038,7 @@
         <f>E35-F35</f>
         <v/>
       </c>
-      <c r="H35" s="15">
+      <c r="H35" s="21">
         <f>IF(E35&gt;0, F35/E35, 0)</f>
         <v/>
       </c>
@@ -4465,7 +5116,7 @@
         <f>E37-F37</f>
         <v/>
       </c>
-      <c r="H37" s="15">
+      <c r="H37" s="21">
         <f>IF(E37&gt;0, F37/E37, 0)</f>
         <v/>
       </c>
@@ -4543,7 +5194,7 @@
         <f>E39-F39</f>
         <v/>
       </c>
-      <c r="H39" s="15">
+      <c r="H39" s="21">
         <f>IF(E39&gt;0, F39/E39, 0)</f>
         <v/>
       </c>
@@ -4621,7 +5272,7 @@
         <f>E41-F41</f>
         <v/>
       </c>
-      <c r="H41" s="15">
+      <c r="H41" s="21">
         <f>IF(E41&gt;0, F41/E41, 0)</f>
         <v/>
       </c>
@@ -4699,7 +5350,7 @@
         <f>E43-F43</f>
         <v/>
       </c>
-      <c r="H43" s="15">
+      <c r="H43" s="21">
         <f>IF(E43&gt;0, F43/E43, 0)</f>
         <v/>
       </c>
@@ -4777,7 +5428,7 @@
         <f>E45-F45</f>
         <v/>
       </c>
-      <c r="H45" s="15">
+      <c r="H45" s="21">
         <f>IF(E45&gt;0, F45/E45, 0)</f>
         <v/>
       </c>
@@ -4855,7 +5506,7 @@
         <f>E47-F47</f>
         <v/>
       </c>
-      <c r="H47" s="15">
+      <c r="H47" s="21">
         <f>IF(E47&gt;0, F47/E47, 0)</f>
         <v/>
       </c>
@@ -4933,7 +5584,7 @@
         <f>E49-F49</f>
         <v/>
       </c>
-      <c r="H49" s="15">
+      <c r="H49" s="21">
         <f>IF(E49&gt;0, F49/E49, 0)</f>
         <v/>
       </c>
@@ -4966,7 +5617,7 @@
         <v>12</v>
       </c>
       <c r="F50" s="19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G50" s="19">
         <f>E50-F50</f>
@@ -4976,9 +5627,9 @@
         <f>IF(E50&gt;0, F50/E50, 0)</f>
         <v/>
       </c>
-      <c r="I50" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="I50" s="33" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5662,7 @@
         <f>E51-F51</f>
         <v/>
       </c>
-      <c r="H51" s="15">
+      <c r="H51" s="21">
         <f>IF(E51&gt;0, F51/E51, 0)</f>
         <v/>
       </c>
@@ -5089,7 +5740,7 @@
         <f>E53-F53</f>
         <v/>
       </c>
-      <c r="H53" s="15">
+      <c r="H53" s="21">
         <f>IF(E53&gt;0, F53/E53, 0)</f>
         <v/>
       </c>
@@ -5167,7 +5818,7 @@
         <f>E55-F55</f>
         <v/>
       </c>
-      <c r="H55" s="15">
+      <c r="H55" s="21">
         <f>IF(E55&gt;0, F55/E55, 0)</f>
         <v/>
       </c>
@@ -5245,7 +5896,7 @@
         <f>E57-F57</f>
         <v/>
       </c>
-      <c r="H57" s="15">
+      <c r="H57" s="21">
         <f>IF(E57&gt;0, F57/E57, 0)</f>
         <v/>
       </c>
@@ -5323,7 +5974,7 @@
         <f>E59-F59</f>
         <v/>
       </c>
-      <c r="H59" s="15">
+      <c r="H59" s="21">
         <f>IF(E59&gt;0, F59/E59, 0)</f>
         <v/>
       </c>
@@ -5401,7 +6052,7 @@
         <f>E61-F61</f>
         <v/>
       </c>
-      <c r="H61" s="15">
+      <c r="H61" s="21">
         <f>IF(E61&gt;0, F61/E61, 0)</f>
         <v/>
       </c>
@@ -5479,7 +6130,7 @@
         <f>E63-F63</f>
         <v/>
       </c>
-      <c r="H63" s="15">
+      <c r="H63" s="21">
         <f>IF(E63&gt;0, F63/E63, 0)</f>
         <v/>
       </c>
@@ -5557,7 +6208,7 @@
         <f>E65-F65</f>
         <v/>
       </c>
-      <c r="H65" s="15">
+      <c r="H65" s="21">
         <f>IF(E65&gt;0, F65/E65, 0)</f>
         <v/>
       </c>
@@ -5635,7 +6286,7 @@
         <f>E67-F67</f>
         <v/>
       </c>
-      <c r="H67" s="15">
+      <c r="H67" s="21">
         <f>IF(E67&gt;0, F67/E67, 0)</f>
         <v/>
       </c>
@@ -5713,7 +6364,7 @@
         <f>E69-F69</f>
         <v/>
       </c>
-      <c r="H69" s="15">
+      <c r="H69" s="21">
         <f>IF(E69&gt;0, F69/E69, 0)</f>
         <v/>
       </c>
@@ -5791,7 +6442,7 @@
         <f>E71-F71</f>
         <v/>
       </c>
-      <c r="H71" s="15">
+      <c r="H71" s="21">
         <f>IF(E71&gt;0, F71/E71, 0)</f>
         <v/>
       </c>
@@ -5869,7 +6520,7 @@
         <f>E73-F73</f>
         <v/>
       </c>
-      <c r="H73" s="15">
+      <c r="H73" s="21">
         <f>IF(E73&gt;0, F73/E73, 0)</f>
         <v/>
       </c>
@@ -5947,7 +6598,7 @@
         <f>E75-F75</f>
         <v/>
       </c>
-      <c r="H75" s="15">
+      <c r="H75" s="21">
         <f>IF(E75&gt;0, F75/E75, 0)</f>
         <v/>
       </c>
@@ -6025,7 +6676,7 @@
         <f>E77-F77</f>
         <v/>
       </c>
-      <c r="H77" s="15">
+      <c r="H77" s="21">
         <f>IF(E77&gt;0, F77/E77, 0)</f>
         <v/>
       </c>
@@ -6103,7 +6754,7 @@
         <f>E79-F79</f>
         <v/>
       </c>
-      <c r="H79" s="15">
+      <c r="H79" s="21">
         <f>IF(E79&gt;0, F79/E79, 0)</f>
         <v/>
       </c>
@@ -6181,7 +6832,7 @@
         <f>E81-F81</f>
         <v/>
       </c>
-      <c r="H81" s="15">
+      <c r="H81" s="21">
         <f>IF(E81&gt;0, F81/E81, 0)</f>
         <v/>
       </c>
@@ -6253,19 +6904,19 @@
         <v>12</v>
       </c>
       <c r="F83" s="13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G83" s="13">
         <f>E83-F83</f>
         <v/>
       </c>
-      <c r="H83" s="15">
+      <c r="H83" s="21">
         <f>IF(E83&gt;0, F83/E83, 0)</f>
         <v/>
       </c>
-      <c r="I83" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="I83" s="33" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
@@ -6337,7 +6988,7 @@
         <f>E85-F85</f>
         <v/>
       </c>
-      <c r="H85" s="15">
+      <c r="H85" s="21">
         <f>IF(E85&gt;0, F85/E85, 0)</f>
         <v/>
       </c>
@@ -6415,7 +7066,7 @@
         <f>E87-F87</f>
         <v/>
       </c>
-      <c r="H87" s="15">
+      <c r="H87" s="21">
         <f>IF(E87&gt;0, F87/E87, 0)</f>
         <v/>
       </c>
@@ -6448,7 +7099,7 @@
         <v>12</v>
       </c>
       <c r="F88" s="19" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G88" s="19">
         <f>E88-F88</f>
@@ -6458,9 +7109,9 @@
         <f>IF(E88&gt;0, F88/E88, 0)</f>
         <v/>
       </c>
-      <c r="I88" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="I88" s="33" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
@@ -6493,7 +7144,7 @@
         <f>E89-F89</f>
         <v/>
       </c>
-      <c r="H89" s="15">
+      <c r="H89" s="21">
         <f>IF(E89&gt;0, F89/E89, 0)</f>
         <v/>
       </c>
@@ -6565,13 +7216,13 @@
         <v>12</v>
       </c>
       <c r="F91" s="13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G91" s="13">
         <f>E91-F91</f>
         <v/>
       </c>
-      <c r="H91" s="15">
+      <c r="H91" s="21">
         <f>IF(E91&gt;0, F91/E91, 0)</f>
         <v/>
       </c>
@@ -6649,7 +7300,7 @@
         <f>E93-F93</f>
         <v/>
       </c>
-      <c r="H93" s="15">
+      <c r="H93" s="21">
         <f>IF(E93&gt;0, F93/E93, 0)</f>
         <v/>
       </c>
@@ -6727,7 +7378,7 @@
         <f>E95-F95</f>
         <v/>
       </c>
-      <c r="H95" s="15">
+      <c r="H95" s="21">
         <f>IF(E95&gt;0, F95/E95, 0)</f>
         <v/>
       </c>
@@ -6805,7 +7456,7 @@
         <f>E97-F97</f>
         <v/>
       </c>
-      <c r="H97" s="15">
+      <c r="H97" s="21">
         <f>IF(E97&gt;0, F97/E97, 0)</f>
         <v/>
       </c>
@@ -6883,7 +7534,7 @@
         <f>E99-F99</f>
         <v/>
       </c>
-      <c r="H99" s="15">
+      <c r="H99" s="21">
         <f>IF(E99&gt;0, F99/E99, 0)</f>
         <v/>
       </c>
@@ -6961,7 +7612,7 @@
         <f>E101-F101</f>
         <v/>
       </c>
-      <c r="H101" s="15">
+      <c r="H101" s="21">
         <f>IF(E101&gt;0, F101/E101, 0)</f>
         <v/>
       </c>
@@ -7039,7 +7690,7 @@
         <f>E103-F103</f>
         <v/>
       </c>
-      <c r="H103" s="15">
+      <c r="H103" s="21">
         <f>IF(E103&gt;0, F103/E103, 0)</f>
         <v/>
       </c>
@@ -7117,7 +7768,7 @@
         <f>E105-F105</f>
         <v/>
       </c>
-      <c r="H105" s="15">
+      <c r="H105" s="21">
         <f>IF(E105&gt;0, F105/E105, 0)</f>
         <v/>
       </c>
@@ -7195,7 +7846,7 @@
         <f>E107-F107</f>
         <v/>
       </c>
-      <c r="H107" s="15">
+      <c r="H107" s="21">
         <f>IF(E107&gt;0, F107/E107, 0)</f>
         <v/>
       </c>
@@ -7273,7 +7924,7 @@
         <f>E109-F109</f>
         <v/>
       </c>
-      <c r="H109" s="15">
+      <c r="H109" s="21">
         <f>IF(E109&gt;0, F109/E109, 0)</f>
         <v/>
       </c>
@@ -7351,7 +8002,7 @@
         <f>E111-F111</f>
         <v/>
       </c>
-      <c r="H111" s="15">
+      <c r="H111" s="21">
         <f>IF(E111&gt;0, F111/E111, 0)</f>
         <v/>
       </c>
@@ -7429,7 +8080,7 @@
         <f>E113-F113</f>
         <v/>
       </c>
-      <c r="H113" s="15">
+      <c r="H113" s="21">
         <f>IF(E113&gt;0, F113/E113, 0)</f>
         <v/>
       </c>
@@ -7507,7 +8158,7 @@
         <f>E115-F115</f>
         <v/>
       </c>
-      <c r="H115" s="15">
+      <c r="H115" s="21">
         <f>IF(E115&gt;0, F115/E115, 0)</f>
         <v/>
       </c>
@@ -7585,7 +8236,7 @@
         <f>E117-F117</f>
         <v/>
       </c>
-      <c r="H117" s="15">
+      <c r="H117" s="21">
         <f>IF(E117&gt;0, F117/E117, 0)</f>
         <v/>
       </c>
@@ -7663,7 +8314,7 @@
         <f>E119-F119</f>
         <v/>
       </c>
-      <c r="H119" s="15">
+      <c r="H119" s="21">
         <f>IF(E119&gt;0, F119/E119, 0)</f>
         <v/>
       </c>
@@ -7696,7 +8347,7 @@
         <v>12</v>
       </c>
       <c r="F120" s="19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G120" s="19">
         <f>E120-F120</f>
@@ -7706,9 +8357,9 @@
         <f>IF(E120&gt;0, F120/E120, 0)</f>
         <v/>
       </c>
-      <c r="I120" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="I120" s="33" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
@@ -7741,7 +8392,7 @@
         <f>E121-F121</f>
         <v/>
       </c>
-      <c r="H121" s="15">
+      <c r="H121" s="21">
         <f>IF(E121&gt;0, F121/E121, 0)</f>
         <v/>
       </c>
@@ -7819,7 +8470,7 @@
         <f>E123-F123</f>
         <v/>
       </c>
-      <c r="H123" s="15">
+      <c r="H123" s="21">
         <f>IF(E123&gt;0, F123/E123, 0)</f>
         <v/>
       </c>
@@ -7897,7 +8548,7 @@
         <f>E125-F125</f>
         <v/>
       </c>
-      <c r="H125" s="15">
+      <c r="H125" s="21">
         <f>IF(E125&gt;0, F125/E125, 0)</f>
         <v/>
       </c>
@@ -7969,13 +8620,13 @@
         <v>12</v>
       </c>
       <c r="F127" s="13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G127" s="13">
         <f>E127-F127</f>
         <v/>
       </c>
-      <c r="H127" s="15">
+      <c r="H127" s="21">
         <f>IF(E127&gt;0, F127/E127, 0)</f>
         <v/>
       </c>
@@ -8053,7 +8704,7 @@
         <f>E129-F129</f>
         <v/>
       </c>
-      <c r="H129" s="15">
+      <c r="H129" s="21">
         <f>IF(E129&gt;0, F129/E129, 0)</f>
         <v/>
       </c>
@@ -8086,7 +8737,7 @@
         <v>12</v>
       </c>
       <c r="F130" s="19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G130" s="19">
         <f>E130-F130</f>
@@ -8125,13 +8776,13 @@
         <v>12</v>
       </c>
       <c r="F131" s="13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G131" s="13">
         <f>E131-F131</f>
         <v/>
       </c>
-      <c r="H131" s="15">
+      <c r="H131" s="21">
         <f>IF(E131&gt;0, F131/E131, 0)</f>
         <v/>
       </c>
@@ -8209,7 +8860,7 @@
         <f>E133-F133</f>
         <v/>
       </c>
-      <c r="H133" s="15">
+      <c r="H133" s="21">
         <f>IF(E133&gt;0, F133/E133, 0)</f>
         <v/>
       </c>
@@ -8287,7 +8938,7 @@
         <f>E135-F135</f>
         <v/>
       </c>
-      <c r="H135" s="15">
+      <c r="H135" s="21">
         <f>IF(E135&gt;0, F135/E135, 0)</f>
         <v/>
       </c>
@@ -8365,7 +9016,7 @@
         <f>E137-F137</f>
         <v/>
       </c>
-      <c r="H137" s="15">
+      <c r="H137" s="21">
         <f>IF(E137&gt;0, F137/E137, 0)</f>
         <v/>
       </c>
@@ -8443,7 +9094,7 @@
         <f>E139-F139</f>
         <v/>
       </c>
-      <c r="H139" s="15">
+      <c r="H139" s="21">
         <f>IF(E139&gt;0, F139/E139, 0)</f>
         <v/>
       </c>
@@ -8521,7 +9172,7 @@
         <f>E141-F141</f>
         <v/>
       </c>
-      <c r="H141" s="15">
+      <c r="H141" s="21">
         <f>IF(E141&gt;0, F141/E141, 0)</f>
         <v/>
       </c>
@@ -8599,7 +9250,7 @@
         <f>E143-F143</f>
         <v/>
       </c>
-      <c r="H143" s="15">
+      <c r="H143" s="21">
         <f>IF(E143&gt;0, F143/E143, 0)</f>
         <v/>
       </c>
@@ -8677,7 +9328,7 @@
         <f>E145-F145</f>
         <v/>
       </c>
-      <c r="H145" s="15">
+      <c r="H145" s="21">
         <f>IF(E145&gt;0, F145/E145, 0)</f>
         <v/>
       </c>
@@ -8755,7 +9406,7 @@
         <f>E147-F147</f>
         <v/>
       </c>
-      <c r="H147" s="15">
+      <c r="H147" s="21">
         <f>IF(E147&gt;0, F147/E147, 0)</f>
         <v/>
       </c>
@@ -8833,7 +9484,7 @@
         <f>E149-F149</f>
         <v/>
       </c>
-      <c r="H149" s="15">
+      <c r="H149" s="21">
         <f>IF(E149&gt;0, F149/E149, 0)</f>
         <v/>
       </c>
@@ -8905,13 +9556,13 @@
         <v>12</v>
       </c>
       <c r="F151" s="13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G151" s="13">
         <f>E151-F151</f>
         <v/>
       </c>
-      <c r="H151" s="15">
+      <c r="H151" s="21">
         <f>IF(E151&gt;0, F151/E151, 0)</f>
         <v/>
       </c>
@@ -8989,7 +9640,7 @@
         <f>E153-F153</f>
         <v/>
       </c>
-      <c r="H153" s="15">
+      <c r="H153" s="21">
         <f>IF(E153&gt;0, F153/E153, 0)</f>
         <v/>
       </c>
@@ -9067,7 +9718,7 @@
         <f>E155-F155</f>
         <v/>
       </c>
-      <c r="H155" s="15">
+      <c r="H155" s="21">
         <f>IF(E155&gt;0, F155/E155, 0)</f>
         <v/>
       </c>
@@ -9145,7 +9796,7 @@
         <f>E157-F157</f>
         <v/>
       </c>
-      <c r="H157" s="15">
+      <c r="H157" s="21">
         <f>IF(E157&gt;0, F157/E157, 0)</f>
         <v/>
       </c>
@@ -9223,7 +9874,7 @@
         <f>E159-F159</f>
         <v/>
       </c>
-      <c r="H159" s="15">
+      <c r="H159" s="21">
         <f>IF(E159&gt;0, F159/E159, 0)</f>
         <v/>
       </c>
@@ -9301,7 +9952,7 @@
         <f>E161-F161</f>
         <v/>
       </c>
-      <c r="H161" s="15">
+      <c r="H161" s="21">
         <f>IF(E161&gt;0, F161/E161, 0)</f>
         <v/>
       </c>
@@ -9379,7 +10030,7 @@
         <f>E163-F163</f>
         <v/>
       </c>
-      <c r="H163" s="15">
+      <c r="H163" s="21">
         <f>IF(E163&gt;0, F163/E163, 0)</f>
         <v/>
       </c>
@@ -9457,7 +10108,7 @@
         <f>E165-F165</f>
         <v/>
       </c>
-      <c r="H165" s="15">
+      <c r="H165" s="21">
         <f>IF(E165&gt;0, F165/E165, 0)</f>
         <v/>
       </c>
@@ -9535,7 +10186,7 @@
         <f>E167-F167</f>
         <v/>
       </c>
-      <c r="H167" s="15">
+      <c r="H167" s="21">
         <f>IF(E167&gt;0, F167/E167, 0)</f>
         <v/>
       </c>
@@ -9613,7 +10264,7 @@
         <f>E169-F169</f>
         <v/>
       </c>
-      <c r="H169" s="15">
+      <c r="H169" s="21">
         <f>IF(E169&gt;0, F169/E169, 0)</f>
         <v/>
       </c>
@@ -9691,7 +10342,7 @@
         <f>E171-F171</f>
         <v/>
       </c>
-      <c r="H171" s="15">
+      <c r="H171" s="21">
         <f>IF(E171&gt;0, F171/E171, 0)</f>
         <v/>
       </c>
@@ -9769,7 +10420,7 @@
         <f>E173-F173</f>
         <v/>
       </c>
-      <c r="H173" s="15">
+      <c r="H173" s="21">
         <f>IF(E173&gt;0, F173/E173, 0)</f>
         <v/>
       </c>
@@ -9847,7 +10498,7 @@
         <f>E175-F175</f>
         <v/>
       </c>
-      <c r="H175" s="15">
+      <c r="H175" s="21">
         <f>IF(E175&gt;0, F175/E175, 0)</f>
         <v/>
       </c>
@@ -9925,7 +10576,7 @@
         <f>E177-F177</f>
         <v/>
       </c>
-      <c r="H177" s="15">
+      <c r="H177" s="21">
         <f>IF(E177&gt;0, F177/E177, 0)</f>
         <v/>
       </c>
@@ -10003,7 +10654,7 @@
         <f>E179-F179</f>
         <v/>
       </c>
-      <c r="H179" s="15">
+      <c r="H179" s="21">
         <f>IF(E179&gt;0, F179/E179, 0)</f>
         <v/>
       </c>
@@ -10033,7 +10684,7 @@
         </is>
       </c>
       <c r="E180" s="19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F180" s="19" t="n">
         <v>0</v>
@@ -10046,9 +10697,9 @@
         <f>IF(E180&gt;0, F180/E180, 0)</f>
         <v/>
       </c>
-      <c r="I180" s="33" t="inlineStr">
-        <is>
-          <t>Completo</t>
+      <c r="I180" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -10072,7 +10723,7 @@
         </is>
       </c>
       <c r="E181" s="13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F181" s="13" t="n">
         <v>0</v>
@@ -10081,13 +10732,13 @@
         <f>E181-F181</f>
         <v/>
       </c>
-      <c r="H181" s="15">
+      <c r="H181" s="21">
         <f>IF(E181&gt;0, F181/E181, 0)</f>
         <v/>
       </c>
-      <c r="I181" s="33" t="inlineStr">
-        <is>
-          <t>Completo</t>
+      <c r="I181" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -10159,7 +10810,7 @@
         <f>E183-F183</f>
         <v/>
       </c>
-      <c r="H183" s="15">
+      <c r="H183" s="21">
         <f>IF(E183&gt;0, F183/E183, 0)</f>
         <v/>
       </c>
@@ -10237,7 +10888,7 @@
         <f>E185-F185</f>
         <v/>
       </c>
-      <c r="H185" s="15">
+      <c r="H185" s="21">
         <f>IF(E185&gt;0, F185/E185, 0)</f>
         <v/>
       </c>
@@ -10267,7 +10918,7 @@
         </is>
       </c>
       <c r="E186" s="19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F186" s="19" t="n">
         <v>0</v>
@@ -10280,9 +10931,9 @@
         <f>IF(E186&gt;0, F186/E186, 0)</f>
         <v/>
       </c>
-      <c r="I186" s="33" t="inlineStr">
-        <is>
-          <t>Completo</t>
+      <c r="I186" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -10315,7 +10966,7 @@
         <f>E187-F187</f>
         <v/>
       </c>
-      <c r="H187" s="15">
+      <c r="H187" s="21">
         <f>IF(E187&gt;0, F187/E187, 0)</f>
         <v/>
       </c>
@@ -10393,7 +11044,7 @@
         <f>E189-F189</f>
         <v/>
       </c>
-      <c r="H189" s="15">
+      <c r="H189" s="21">
         <f>IF(E189&gt;0, F189/E189, 0)</f>
         <v/>
       </c>
@@ -10471,7 +11122,7 @@
         <f>E191-F191</f>
         <v/>
       </c>
-      <c r="H191" s="15">
+      <c r="H191" s="21">
         <f>IF(E191&gt;0, F191/E191, 0)</f>
         <v/>
       </c>
@@ -10549,7 +11200,7 @@
         <f>E193-F193</f>
         <v/>
       </c>
-      <c r="H193" s="15">
+      <c r="H193" s="21">
         <f>IF(E193&gt;0, F193/E193, 0)</f>
         <v/>
       </c>
@@ -10627,7 +11278,7 @@
         <f>E195-F195</f>
         <v/>
       </c>
-      <c r="H195" s="15">
+      <c r="H195" s="21">
         <f>IF(E195&gt;0, F195/E195, 0)</f>
         <v/>
       </c>
@@ -10705,7 +11356,7 @@
         <f>E197-F197</f>
         <v/>
       </c>
-      <c r="H197" s="15">
+      <c r="H197" s="21">
         <f>IF(E197&gt;0, F197/E197, 0)</f>
         <v/>
       </c>
@@ -10783,7 +11434,7 @@
         <f>E199-F199</f>
         <v/>
       </c>
-      <c r="H199" s="15">
+      <c r="H199" s="21">
         <f>IF(E199&gt;0, F199/E199, 0)</f>
         <v/>
       </c>
@@ -10861,7 +11512,7 @@
         <f>E201-F201</f>
         <v/>
       </c>
-      <c r="H201" s="15">
+      <c r="H201" s="21">
         <f>IF(E201&gt;0, F201/E201, 0)</f>
         <v/>
       </c>
@@ -10939,7 +11590,7 @@
         <f>E203-F203</f>
         <v/>
       </c>
-      <c r="H203" s="15">
+      <c r="H203" s="21">
         <f>IF(E203&gt;0, F203/E203, 0)</f>
         <v/>
       </c>
@@ -11017,7 +11668,7 @@
         <f>E205-F205</f>
         <v/>
       </c>
-      <c r="H205" s="15">
+      <c r="H205" s="21">
         <f>IF(E205&gt;0, F205/E205, 0)</f>
         <v/>
       </c>
@@ -11095,7 +11746,7 @@
         <f>E207-F207</f>
         <v/>
       </c>
-      <c r="H207" s="15">
+      <c r="H207" s="21">
         <f>IF(E207&gt;0, F207/E207, 0)</f>
         <v/>
       </c>
@@ -11173,7 +11824,7 @@
         <f>E209-F209</f>
         <v/>
       </c>
-      <c r="H209" s="15">
+      <c r="H209" s="21">
         <f>IF(E209&gt;0, F209/E209, 0)</f>
         <v/>
       </c>
@@ -11251,7 +11902,7 @@
         <f>E211-F211</f>
         <v/>
       </c>
-      <c r="H211" s="15">
+      <c r="H211" s="21">
         <f>IF(E211&gt;0, F211/E211, 0)</f>
         <v/>
       </c>
@@ -11329,7 +11980,7 @@
         <f>E213-F213</f>
         <v/>
       </c>
-      <c r="H213" s="15">
+      <c r="H213" s="21">
         <f>IF(E213&gt;0, F213/E213, 0)</f>
         <v/>
       </c>
@@ -11407,7 +12058,7 @@
         <f>E215-F215</f>
         <v/>
       </c>
-      <c r="H215" s="15">
+      <c r="H215" s="21">
         <f>IF(E215&gt;0, F215/E215, 0)</f>
         <v/>
       </c>
@@ -11485,7 +12136,7 @@
         <f>E217-F217</f>
         <v/>
       </c>
-      <c r="H217" s="15">
+      <c r="H217" s="21">
         <f>IF(E217&gt;0, F217/E217, 0)</f>
         <v/>
       </c>
@@ -11563,7 +12214,7 @@
         <f>E219-F219</f>
         <v/>
       </c>
-      <c r="H219" s="15">
+      <c r="H219" s="21">
         <f>IF(E219&gt;0, F219/E219, 0)</f>
         <v/>
       </c>
@@ -11641,7 +12292,7 @@
         <f>E221-F221</f>
         <v/>
       </c>
-      <c r="H221" s="15">
+      <c r="H221" s="21">
         <f>IF(E221&gt;0, F221/E221, 0)</f>
         <v/>
       </c>
@@ -11719,7 +12370,7 @@
         <f>E223-F223</f>
         <v/>
       </c>
-      <c r="H223" s="15">
+      <c r="H223" s="21">
         <f>IF(E223&gt;0, F223/E223, 0)</f>
         <v/>
       </c>
@@ -11752,7 +12403,7 @@
         <v>12</v>
       </c>
       <c r="F224" s="19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G224" s="19">
         <f>E224-F224</f>
@@ -11762,9 +12413,9 @@
         <f>IF(E224&gt;0, F224/E224, 0)</f>
         <v/>
       </c>
-      <c r="I224" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="I224" s="33" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
@@ -11797,7 +12448,7 @@
         <f>E225-F225</f>
         <v/>
       </c>
-      <c r="H225" s="15">
+      <c r="H225" s="21">
         <f>IF(E225&gt;0, F225/E225, 0)</f>
         <v/>
       </c>
@@ -11875,7 +12526,7 @@
         <f>E227-F227</f>
         <v/>
       </c>
-      <c r="H227" s="15">
+      <c r="H227" s="21">
         <f>IF(E227&gt;0, F227/E227, 0)</f>
         <v/>
       </c>
@@ -11953,7 +12604,7 @@
         <f>E229-F229</f>
         <v/>
       </c>
-      <c r="H229" s="15">
+      <c r="H229" s="21">
         <f>IF(E229&gt;0, F229/E229, 0)</f>
         <v/>
       </c>
@@ -12025,19 +12676,19 @@
         <v>12</v>
       </c>
       <c r="F231" s="13" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G231" s="13">
         <f>E231-F231</f>
         <v/>
       </c>
-      <c r="H231" s="15">
+      <c r="H231" s="21">
         <f>IF(E231&gt;0, F231/E231, 0)</f>
         <v/>
       </c>
-      <c r="I231" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="I231" s="33" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
@@ -12109,7 +12760,7 @@
         <f>E233-F233</f>
         <v/>
       </c>
-      <c r="H233" s="15">
+      <c r="H233" s="21">
         <f>IF(E233&gt;0, F233/E233, 0)</f>
         <v/>
       </c>
@@ -12187,7 +12838,7 @@
         <f>E235-F235</f>
         <v/>
       </c>
-      <c r="H235" s="15">
+      <c r="H235" s="21">
         <f>IF(E235&gt;0, F235/E235, 0)</f>
         <v/>
       </c>
@@ -12265,7 +12916,7 @@
         <f>E237-F237</f>
         <v/>
       </c>
-      <c r="H237" s="15">
+      <c r="H237" s="21">
         <f>IF(E237&gt;0, F237/E237, 0)</f>
         <v/>
       </c>
@@ -12337,13 +12988,13 @@
         <v>12</v>
       </c>
       <c r="F239" s="13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G239" s="13">
         <f>E239-F239</f>
         <v/>
       </c>
-      <c r="H239" s="15">
+      <c r="H239" s="21">
         <f>IF(E239&gt;0, F239/E239, 0)</f>
         <v/>
       </c>
@@ -12376,7 +13027,7 @@
         <v>12</v>
       </c>
       <c r="F240" s="19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G240" s="19">
         <f>E240-F240</f>
@@ -12386,9 +13037,9 @@
         <f>IF(E240&gt;0, F240/E240, 0)</f>
         <v/>
       </c>
-      <c r="I240" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="I240" s="33" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
@@ -12415,13 +13066,13 @@
         <v>12</v>
       </c>
       <c r="F241" s="13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G241" s="13">
         <f>E241-F241</f>
         <v/>
       </c>
-      <c r="H241" s="15">
+      <c r="H241" s="21">
         <f>IF(E241&gt;0, F241/E241, 0)</f>
         <v/>
       </c>
@@ -12499,7 +13150,7 @@
         <f>E243-F243</f>
         <v/>
       </c>
-      <c r="H243" s="15">
+      <c r="H243" s="21">
         <f>IF(E243&gt;0, F243/E243, 0)</f>
         <v/>
       </c>
@@ -12532,7 +13183,7 @@
         <v>12</v>
       </c>
       <c r="F244" s="19" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G244" s="19">
         <f>E244-F244</f>
@@ -12542,9 +13193,9 @@
         <f>IF(E244&gt;0, F244/E244, 0)</f>
         <v/>
       </c>
-      <c r="I244" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="I244" s="33" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
@@ -12577,7 +13228,7 @@
         <f>E245-F245</f>
         <v/>
       </c>
-      <c r="H245" s="15">
+      <c r="H245" s="21">
         <f>IF(E245&gt;0, F245/E245, 0)</f>
         <v/>
       </c>
@@ -12655,7 +13306,7 @@
         <f>E247-F247</f>
         <v/>
       </c>
-      <c r="H247" s="15">
+      <c r="H247" s="21">
         <f>IF(E247&gt;0, F247/E247, 0)</f>
         <v/>
       </c>
@@ -12688,7 +13339,7 @@
         <v>12</v>
       </c>
       <c r="F248" s="19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G248" s="19">
         <f>E248-F248</f>
@@ -12698,9 +13349,9 @@
         <f>IF(E248&gt;0, F248/E248, 0)</f>
         <v/>
       </c>
-      <c r="I248" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="I248" s="33" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
@@ -12733,7 +13384,7 @@
         <f>E249-F249</f>
         <v/>
       </c>
-      <c r="H249" s="15">
+      <c r="H249" s="21">
         <f>IF(E249&gt;0, F249/E249, 0)</f>
         <v/>
       </c>
@@ -12766,7 +13417,7 @@
         <v>12</v>
       </c>
       <c r="F250" s="19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G250" s="19">
         <f>E250-F250</f>
@@ -12811,7 +13462,7 @@
         <f>E251-F251</f>
         <v/>
       </c>
-      <c r="H251" s="15">
+      <c r="H251" s="21">
         <f>IF(E251&gt;0, F251/E251, 0)</f>
         <v/>
       </c>
@@ -12844,7 +13495,7 @@
         <v>12</v>
       </c>
       <c r="F252" s="19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G252" s="19">
         <f>E252-F252</f>
@@ -12854,9 +13505,9 @@
         <f>IF(E252&gt;0, F252/E252, 0)</f>
         <v/>
       </c>
-      <c r="I252" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="I252" s="33" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
@@ -12883,19 +13534,19 @@
         <v>12</v>
       </c>
       <c r="F253" s="13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G253" s="13">
         <f>E253-F253</f>
         <v/>
       </c>
-      <c r="H253" s="15">
+      <c r="H253" s="21">
         <f>IF(E253&gt;0, F253/E253, 0)</f>
         <v/>
       </c>
-      <c r="I253" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="I253" s="33" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
@@ -12922,7 +13573,7 @@
         <v>12</v>
       </c>
       <c r="F254" s="19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G254" s="19">
         <f>E254-F254</f>
@@ -12932,9 +13583,9 @@
         <f>IF(E254&gt;0, F254/E254, 0)</f>
         <v/>
       </c>
-      <c r="I254" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="I254" s="33" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
@@ -12967,7 +13618,7 @@
         <f>E255-F255</f>
         <v/>
       </c>
-      <c r="H255" s="15">
+      <c r="H255" s="21">
         <f>IF(E255&gt;0, F255/E255, 0)</f>
         <v/>
       </c>
@@ -13039,13 +13690,13 @@
         <v>12</v>
       </c>
       <c r="F257" s="13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G257" s="13">
         <f>E257-F257</f>
         <v/>
       </c>
-      <c r="H257" s="15">
+      <c r="H257" s="21">
         <f>IF(E257&gt;0, F257/E257, 0)</f>
         <v/>
       </c>
@@ -13078,7 +13729,7 @@
         <v>12</v>
       </c>
       <c r="F258" s="19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G258" s="19">
         <f>E258-F258</f>
@@ -13117,13 +13768,13 @@
         <v>12</v>
       </c>
       <c r="F259" s="13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G259" s="13">
         <f>E259-F259</f>
         <v/>
       </c>
-      <c r="H259" s="15">
+      <c r="H259" s="21">
         <f>IF(E259&gt;0, F259/E259, 0)</f>
         <v/>
       </c>
@@ -13156,7 +13807,7 @@
         <v>12</v>
       </c>
       <c r="F260" s="19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G260" s="19">
         <f>E260-F260</f>
@@ -13201,7 +13852,7 @@
         <f>E261-F261</f>
         <v/>
       </c>
-      <c r="H261" s="15">
+      <c r="H261" s="21">
         <f>IF(E261&gt;0, F261/E261, 0)</f>
         <v/>
       </c>
@@ -13234,7 +13885,7 @@
         <v>12</v>
       </c>
       <c r="F262" s="19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G262" s="19">
         <f>E262-F262</f>
@@ -13273,13 +13924,13 @@
         <v>12</v>
       </c>
       <c r="F263" s="13" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G263" s="13">
         <f>E263-F263</f>
         <v/>
       </c>
-      <c r="H263" s="15">
+      <c r="H263" s="21">
         <f>IF(E263&gt;0, F263/E263, 0)</f>
         <v/>
       </c>
@@ -13312,7 +13963,7 @@
         <v>12</v>
       </c>
       <c r="F264" s="19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G264" s="19">
         <f>E264-F264</f>
@@ -13322,9 +13973,9 @@
         <f>IF(E264&gt;0, F264/E264, 0)</f>
         <v/>
       </c>
-      <c r="I264" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="I264" s="33" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
@@ -13351,13 +14002,13 @@
         <v>12</v>
       </c>
       <c r="F265" s="13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G265" s="13">
         <f>E265-F265</f>
         <v/>
       </c>
-      <c r="H265" s="15">
+      <c r="H265" s="21">
         <f>IF(E265&gt;0, F265/E265, 0)</f>
         <v/>
       </c>
@@ -13390,7 +14041,7 @@
         <v>12</v>
       </c>
       <c r="F266" s="19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G266" s="19">
         <f>E266-F266</f>
@@ -13400,9 +14051,9 @@
         <f>IF(E266&gt;0, F266/E266, 0)</f>
         <v/>
       </c>
-      <c r="I266" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="I266" s="33" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
@@ -13429,13 +14080,13 @@
         <v>12</v>
       </c>
       <c r="F267" s="13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G267" s="13">
         <f>E267-F267</f>
         <v/>
       </c>
-      <c r="H267" s="15">
+      <c r="H267" s="21">
         <f>IF(E267&gt;0, F267/E267, 0)</f>
         <v/>
       </c>
@@ -13468,7 +14119,7 @@
         <v>12</v>
       </c>
       <c r="F268" s="19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G268" s="19">
         <f>E268-F268</f>
@@ -13507,19 +14158,19 @@
         <v>12</v>
       </c>
       <c r="F269" s="13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G269" s="13">
         <f>E269-F269</f>
         <v/>
       </c>
-      <c r="H269" s="15">
+      <c r="H269" s="21">
         <f>IF(E269&gt;0, F269/E269, 0)</f>
         <v/>
       </c>
-      <c r="I269" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="I269" s="33" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
@@ -13546,7 +14197,7 @@
         <v>12</v>
       </c>
       <c r="F270" s="19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G270" s="19">
         <f>E270-F270</f>
@@ -13591,7 +14242,7 @@
         <f>E271-F271</f>
         <v/>
       </c>
-      <c r="H271" s="15">
+      <c r="H271" s="21">
         <f>IF(E271&gt;0, F271/E271, 0)</f>
         <v/>
       </c>
@@ -13624,7 +14275,7 @@
         <v>12</v>
       </c>
       <c r="F272" s="19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G272" s="19">
         <f>E272-F272</f>
@@ -13669,7 +14320,7 @@
         <f>E273-F273</f>
         <v/>
       </c>
-      <c r="H273" s="15">
+      <c r="H273" s="21">
         <f>IF(E273&gt;0, F273/E273, 0)</f>
         <v/>
       </c>
@@ -13741,13 +14392,13 @@
         <v>12</v>
       </c>
       <c r="F275" s="13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G275" s="13">
         <f>E275-F275</f>
         <v/>
       </c>
-      <c r="H275" s="15">
+      <c r="H275" s="21">
         <f>IF(E275&gt;0, F275/E275, 0)</f>
         <v/>
       </c>
@@ -13780,7 +14431,7 @@
         <v>12</v>
       </c>
       <c r="F276" s="19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G276" s="19">
         <f>E276-F276</f>
@@ -13825,7 +14476,7 @@
         <f>E277-F277</f>
         <v/>
       </c>
-      <c r="H277" s="15">
+      <c r="H277" s="21">
         <f>IF(E277&gt;0, F277/E277, 0)</f>
         <v/>
       </c>
@@ -13903,7 +14554,7 @@
         <f>E279-F279</f>
         <v/>
       </c>
-      <c r="H279" s="15">
+      <c r="H279" s="21">
         <f>IF(E279&gt;0, F279/E279, 0)</f>
         <v/>
       </c>
@@ -13936,7 +14587,7 @@
         <v>12</v>
       </c>
       <c r="F280" s="19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G280" s="19">
         <f>E280-F280</f>
@@ -13975,13 +14626,13 @@
         <v>12</v>
       </c>
       <c r="F281" s="13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G281" s="13">
         <f>E281-F281</f>
         <v/>
       </c>
-      <c r="H281" s="15">
+      <c r="H281" s="21">
         <f>IF(E281&gt;0, F281/E281, 0)</f>
         <v/>
       </c>
@@ -14059,7 +14710,7 @@
         <f>E283-F283</f>
         <v/>
       </c>
-      <c r="H283" s="15">
+      <c r="H283" s="21">
         <f>IF(E283&gt;0, F283/E283, 0)</f>
         <v/>
       </c>
@@ -14092,7 +14743,7 @@
         <v>12</v>
       </c>
       <c r="F284" s="19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G284" s="19">
         <f>E284-F284</f>
@@ -14102,9 +14753,9 @@
         <f>IF(E284&gt;0, F284/E284, 0)</f>
         <v/>
       </c>
-      <c r="I284" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="I284" s="33" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
@@ -14131,19 +14782,19 @@
         <v>12</v>
       </c>
       <c r="F285" s="13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G285" s="13">
         <f>E285-F285</f>
         <v/>
       </c>
-      <c r="H285" s="15">
+      <c r="H285" s="21">
         <f>IF(E285&gt;0, F285/E285, 0)</f>
         <v/>
       </c>
-      <c r="I285" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="I285" s="33" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
@@ -14170,7 +14821,7 @@
         <v>12</v>
       </c>
       <c r="F286" s="19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G286" s="19">
         <f>E286-F286</f>
@@ -14180,9 +14831,9 @@
         <f>IF(E286&gt;0, F286/E286, 0)</f>
         <v/>
       </c>
-      <c r="I286" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="I286" s="33" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
@@ -14209,19 +14860,19 @@
         <v>12</v>
       </c>
       <c r="F287" s="13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G287" s="13">
         <f>E287-F287</f>
         <v/>
       </c>
-      <c r="H287" s="15">
+      <c r="H287" s="21">
         <f>IF(E287&gt;0, F287/E287, 0)</f>
         <v/>
       </c>
-      <c r="I287" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="I287" s="33" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
@@ -14287,13 +14938,13 @@
         <v>12</v>
       </c>
       <c r="F289" s="13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G289" s="13">
         <f>E289-F289</f>
         <v/>
       </c>
-      <c r="H289" s="15">
+      <c r="H289" s="21">
         <f>IF(E289&gt;0, F289/E289, 0)</f>
         <v/>
       </c>
@@ -14326,7 +14977,7 @@
         <v>12</v>
       </c>
       <c r="F290" s="19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G290" s="19">
         <f>E290-F290</f>
@@ -14336,9 +14987,9 @@
         <f>IF(E290&gt;0, F290/E290, 0)</f>
         <v/>
       </c>
-      <c r="I290" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="I290" s="33" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
@@ -14365,19 +15016,19 @@
         <v>12</v>
       </c>
       <c r="F291" s="13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G291" s="13">
         <f>E291-F291</f>
         <v/>
       </c>
-      <c r="H291" s="15">
+      <c r="H291" s="21">
         <f>IF(E291&gt;0, F291/E291, 0)</f>
         <v/>
       </c>
-      <c r="I291" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="I291" s="33" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
@@ -14404,7 +15055,7 @@
         <v>12</v>
       </c>
       <c r="F292" s="19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G292" s="19">
         <f>E292-F292</f>
@@ -14449,7 +15100,7 @@
         <f>E293-F293</f>
         <v/>
       </c>
-      <c r="H293" s="15">
+      <c r="H293" s="21">
         <f>IF(E293&gt;0, F293/E293, 0)</f>
         <v/>
       </c>
@@ -14482,7 +15133,7 @@
         <v>12</v>
       </c>
       <c r="F294" s="19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G294" s="19">
         <f>E294-F294</f>
@@ -14492,9 +15143,9 @@
         <f>IF(E294&gt;0, F294/E294, 0)</f>
         <v/>
       </c>
-      <c r="I294" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="I294" s="33" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
@@ -14521,19 +15172,19 @@
         <v>12</v>
       </c>
       <c r="F295" s="13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G295" s="13">
         <f>E295-F295</f>
         <v/>
       </c>
-      <c r="H295" s="15">
+      <c r="H295" s="21">
         <f>IF(E295&gt;0, F295/E295, 0)</f>
         <v/>
       </c>
-      <c r="I295" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="I295" s="33" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
@@ -14560,7 +15211,7 @@
         <v>12</v>
       </c>
       <c r="F296" s="19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G296" s="19">
         <f>E296-F296</f>
@@ -14599,19 +15250,19 @@
         <v>12</v>
       </c>
       <c r="F297" s="13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G297" s="13">
         <f>E297-F297</f>
         <v/>
       </c>
-      <c r="H297" s="15">
+      <c r="H297" s="21">
         <f>IF(E297&gt;0, F297/E297, 0)</f>
         <v/>
       </c>
-      <c r="I297" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="I297" s="33" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
@@ -14677,13 +15328,13 @@
         <v>12</v>
       </c>
       <c r="F299" s="13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G299" s="13">
         <f>E299-F299</f>
         <v/>
       </c>
-      <c r="H299" s="15">
+      <c r="H299" s="21">
         <f>IF(E299&gt;0, F299/E299, 0)</f>
         <v/>
       </c>
@@ -14716,7 +15367,7 @@
         <v>12</v>
       </c>
       <c r="F300" s="19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G300" s="19">
         <f>E300-F300</f>
@@ -14755,13 +15406,13 @@
         <v>12</v>
       </c>
       <c r="F301" s="13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G301" s="13">
         <f>E301-F301</f>
         <v/>
       </c>
-      <c r="H301" s="15">
+      <c r="H301" s="21">
         <f>IF(E301&gt;0, F301/E301, 0)</f>
         <v/>
       </c>
@@ -14833,13 +15484,13 @@
         <v>12</v>
       </c>
       <c r="F303" s="13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G303" s="13">
         <f>E303-F303</f>
         <v/>
       </c>
-      <c r="H303" s="15">
+      <c r="H303" s="21">
         <f>IF(E303&gt;0, F303/E303, 0)</f>
         <v/>
       </c>
@@ -14872,7 +15523,7 @@
         <v>12</v>
       </c>
       <c r="F304" s="19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G304" s="19">
         <f>E304-F304</f>
@@ -14911,13 +15562,13 @@
         <v>12</v>
       </c>
       <c r="F305" s="13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G305" s="13">
         <f>E305-F305</f>
         <v/>
       </c>
-      <c r="H305" s="15">
+      <c r="H305" s="21">
         <f>IF(E305&gt;0, F305/E305, 0)</f>
         <v/>
       </c>
@@ -14989,19 +15640,19 @@
         <v>12</v>
       </c>
       <c r="F307" s="13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G307" s="13">
         <f>E307-F307</f>
         <v/>
       </c>
-      <c r="H307" s="15">
+      <c r="H307" s="21">
         <f>IF(E307&gt;0, F307/E307, 0)</f>
         <v/>
       </c>
-      <c r="I307" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="I307" s="33" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
@@ -15028,7 +15679,7 @@
         <v>12</v>
       </c>
       <c r="F308" s="19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G308" s="19">
         <f>E308-F308</f>
@@ -15067,13 +15718,13 @@
         <v>12</v>
       </c>
       <c r="F309" s="13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G309" s="13">
         <f>E309-F309</f>
         <v/>
       </c>
-      <c r="H309" s="15">
+      <c r="H309" s="21">
         <f>IF(E309&gt;0, F309/E309, 0)</f>
         <v/>
       </c>
@@ -15145,19 +15796,19 @@
         <v>12</v>
       </c>
       <c r="F311" s="13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G311" s="13">
         <f>E311-F311</f>
         <v/>
       </c>
-      <c r="H311" s="15">
+      <c r="H311" s="21">
         <f>IF(E311&gt;0, F311/E311, 0)</f>
         <v/>
       </c>
-      <c r="I311" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="I311" s="33" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
@@ -15223,13 +15874,13 @@
         <v>12</v>
       </c>
       <c r="F313" s="13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G313" s="13">
         <f>E313-F313</f>
         <v/>
       </c>
-      <c r="H313" s="15">
+      <c r="H313" s="21">
         <f>IF(E313&gt;0, F313/E313, 0)</f>
         <v/>
       </c>
@@ -15262,7 +15913,7 @@
         <v>12</v>
       </c>
       <c r="F314" s="19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G314" s="19">
         <f>E314-F314</f>
@@ -15307,7 +15958,7 @@
         <f>E315-F315</f>
         <v/>
       </c>
-      <c r="H315" s="15">
+      <c r="H315" s="21">
         <f>IF(E315&gt;0, F315/E315, 0)</f>
         <v/>
       </c>
@@ -15379,19 +16030,19 @@
         <v>12</v>
       </c>
       <c r="F317" s="13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G317" s="13">
         <f>E317-F317</f>
         <v/>
       </c>
-      <c r="H317" s="15">
+      <c r="H317" s="21">
         <f>IF(E317&gt;0, F317/E317, 0)</f>
         <v/>
       </c>
-      <c r="I317" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="I317" s="33" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
@@ -15418,7 +16069,7 @@
         <v>12</v>
       </c>
       <c r="F318" s="19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G318" s="19">
         <f>E318-F318</f>
@@ -15428,9 +16079,9 @@
         <f>IF(E318&gt;0, F318/E318, 0)</f>
         <v/>
       </c>
-      <c r="I318" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="I318" s="33" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
@@ -15457,19 +16108,19 @@
         <v>12</v>
       </c>
       <c r="F319" s="13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G319" s="13">
         <f>E319-F319</f>
         <v/>
       </c>
-      <c r="H319" s="15">
+      <c r="H319" s="21">
         <f>IF(E319&gt;0, F319/E319, 0)</f>
         <v/>
       </c>
-      <c r="I319" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="I319" s="33" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
@@ -15496,7 +16147,7 @@
         <v>12</v>
       </c>
       <c r="F320" s="19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G320" s="19">
         <f>E320-F320</f>
@@ -15506,9 +16157,9 @@
         <f>IF(E320&gt;0, F320/E320, 0)</f>
         <v/>
       </c>
-      <c r="I320" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="I320" s="33" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
@@ -15541,7 +16192,7 @@
         <f>E321-F321</f>
         <v/>
       </c>
-      <c r="H321" s="15">
+      <c r="H321" s="21">
         <f>IF(E321&gt;0, F321/E321, 0)</f>
         <v/>
       </c>
@@ -15574,7 +16225,7 @@
         <v>12</v>
       </c>
       <c r="F322" s="19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G322" s="19">
         <f>E322-F322</f>
@@ -15584,9 +16235,9 @@
         <f>IF(E322&gt;0, F322/E322, 0)</f>
         <v/>
       </c>
-      <c r="I322" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="I322" s="33" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
@@ -15619,7 +16270,7 @@
         <f>E323-F323</f>
         <v/>
       </c>
-      <c r="H323" s="15">
+      <c r="H323" s="21">
         <f>IF(E323&gt;0, F323/E323, 0)</f>
         <v/>
       </c>
@@ -15691,13 +16342,13 @@
         <v>12</v>
       </c>
       <c r="F325" s="13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G325" s="13">
         <f>E325-F325</f>
         <v/>
       </c>
-      <c r="H325" s="15">
+      <c r="H325" s="21">
         <f>IF(E325&gt;0, F325/E325, 0)</f>
         <v/>
       </c>
@@ -15775,7 +16426,7 @@
         <f>E327-F327</f>
         <v/>
       </c>
-      <c r="H327" s="15">
+      <c r="H327" s="21">
         <f>IF(E327&gt;0, F327/E327, 0)</f>
         <v/>
       </c>
@@ -15853,7 +16504,7 @@
         <f>E329-F329</f>
         <v/>
       </c>
-      <c r="H329" s="15">
+      <c r="H329" s="21">
         <f>IF(E329&gt;0, F329/E329, 0)</f>
         <v/>
       </c>
@@ -15931,7 +16582,7 @@
         <f>E331-F331</f>
         <v/>
       </c>
-      <c r="H331" s="15">
+      <c r="H331" s="21">
         <f>IF(E331&gt;0, F331/E331, 0)</f>
         <v/>
       </c>
@@ -16009,7 +16660,7 @@
         <f>E333-F333</f>
         <v/>
       </c>
-      <c r="H333" s="15">
+      <c r="H333" s="21">
         <f>IF(E333&gt;0, F333/E333, 0)</f>
         <v/>
       </c>
@@ -16087,7 +16738,7 @@
         <f>E335-F335</f>
         <v/>
       </c>
-      <c r="H335" s="15">
+      <c r="H335" s="21">
         <f>IF(E335&gt;0, F335/E335, 0)</f>
         <v/>
       </c>
@@ -16100,11 +16751,11 @@
     <row r="336" ht="20" customHeight="1">
       <c r="A336" s="16" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B336" s="34" t="n">
-        <v>3695</v>
+        <v>3731</v>
       </c>
       <c r="C336" s="18" t="inlineStr">
         <is>
@@ -16113,7 +16764,7 @@
       </c>
       <c r="D336" s="18" t="inlineStr">
         <is>
-          <t>VINO</t>
+          <t>BEIGE</t>
         </is>
       </c>
       <c r="E336" s="19" t="n">
@@ -16139,11 +16790,11 @@
     <row r="337" ht="20" customHeight="1">
       <c r="A337" s="10" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B337" s="32" t="n">
-        <v>3696</v>
+        <v>3732</v>
       </c>
       <c r="C337" s="12" t="inlineStr">
         <is>
@@ -16152,7 +16803,7 @@
       </c>
       <c r="D337" s="12" t="inlineStr">
         <is>
-          <t>VINO</t>
+          <t>BEIGE</t>
         </is>
       </c>
       <c r="E337" s="13" t="n">
@@ -16165,7 +16816,7 @@
         <f>E337-F337</f>
         <v/>
       </c>
-      <c r="H337" s="15">
+      <c r="H337" s="21">
         <f>IF(E337&gt;0, F337/E337, 0)</f>
         <v/>
       </c>
@@ -16178,11 +16829,11 @@
     <row r="338" ht="20" customHeight="1">
       <c r="A338" s="16" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B338" s="34" t="n">
-        <v>3697</v>
+        <v>3733</v>
       </c>
       <c r="C338" s="18" t="inlineStr">
         <is>
@@ -16191,7 +16842,7 @@
       </c>
       <c r="D338" s="18" t="inlineStr">
         <is>
-          <t>VINO</t>
+          <t>BEIGE</t>
         </is>
       </c>
       <c r="E338" s="19" t="n">
@@ -16217,11 +16868,11 @@
     <row r="339" ht="20" customHeight="1">
       <c r="A339" s="10" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B339" s="32" t="n">
-        <v>3698</v>
+        <v>3734</v>
       </c>
       <c r="C339" s="12" t="inlineStr">
         <is>
@@ -16230,7 +16881,7 @@
       </c>
       <c r="D339" s="12" t="inlineStr">
         <is>
-          <t>VINO</t>
+          <t>BEIGE</t>
         </is>
       </c>
       <c r="E339" s="13" t="n">
@@ -16243,7 +16894,7 @@
         <f>E339-F339</f>
         <v/>
       </c>
-      <c r="H339" s="15">
+      <c r="H339" s="21">
         <f>IF(E339&gt;0, F339/E339, 0)</f>
         <v/>
       </c>
@@ -16256,11 +16907,11 @@
     <row r="340" ht="20" customHeight="1">
       <c r="A340" s="16" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B340" s="34" t="n">
-        <v>3699</v>
+        <v>3735</v>
       </c>
       <c r="C340" s="18" t="inlineStr">
         <is>
@@ -16269,7 +16920,7 @@
       </c>
       <c r="D340" s="18" t="inlineStr">
         <is>
-          <t>VINO</t>
+          <t>BEIGE</t>
         </is>
       </c>
       <c r="E340" s="19" t="n">
@@ -16295,11 +16946,11 @@
     <row r="341" ht="20" customHeight="1">
       <c r="A341" s="10" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B341" s="32" t="n">
-        <v>3700</v>
+        <v>3736</v>
       </c>
       <c r="C341" s="12" t="inlineStr">
         <is>
@@ -16308,7 +16959,7 @@
       </c>
       <c r="D341" s="12" t="inlineStr">
         <is>
-          <t>VINO</t>
+          <t>BEIGE</t>
         </is>
       </c>
       <c r="E341" s="13" t="n">
@@ -16321,7 +16972,7 @@
         <f>E341-F341</f>
         <v/>
       </c>
-      <c r="H341" s="15">
+      <c r="H341" s="21">
         <f>IF(E341&gt;0, F341/E341, 0)</f>
         <v/>
       </c>
@@ -16331,32 +16982,2177 @@
         </is>
       </c>
     </row>
-    <row r="342" ht="24" customHeight="1">
-      <c r="A342" s="24" t="inlineStr">
+    <row r="342" ht="20" customHeight="1">
+      <c r="A342" s="16" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B342" s="34" t="n">
+        <v>3695</v>
+      </c>
+      <c r="C342" s="18" t="inlineStr">
+        <is>
+          <t>MAFER</t>
+        </is>
+      </c>
+      <c r="D342" s="18" t="inlineStr">
+        <is>
+          <t>VINO</t>
+        </is>
+      </c>
+      <c r="E342" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F342" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G342" s="19">
+        <f>E342-F342</f>
+        <v/>
+      </c>
+      <c r="H342" s="35">
+        <f>IF(E342&gt;0, F342/E342, 0)</f>
+        <v/>
+      </c>
+      <c r="I342" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="20" customHeight="1">
+      <c r="A343" s="10" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B343" s="32" t="n">
+        <v>3696</v>
+      </c>
+      <c r="C343" s="12" t="inlineStr">
+        <is>
+          <t>MAFER</t>
+        </is>
+      </c>
+      <c r="D343" s="12" t="inlineStr">
+        <is>
+          <t>VINO</t>
+        </is>
+      </c>
+      <c r="E343" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F343" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G343" s="13">
+        <f>E343-F343</f>
+        <v/>
+      </c>
+      <c r="H343" s="21">
+        <f>IF(E343&gt;0, F343/E343, 0)</f>
+        <v/>
+      </c>
+      <c r="I343" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="20" customHeight="1">
+      <c r="A344" s="16" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B344" s="34" t="n">
+        <v>3697</v>
+      </c>
+      <c r="C344" s="18" t="inlineStr">
+        <is>
+          <t>MAFER</t>
+        </is>
+      </c>
+      <c r="D344" s="18" t="inlineStr">
+        <is>
+          <t>VINO</t>
+        </is>
+      </c>
+      <c r="E344" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F344" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G344" s="19">
+        <f>E344-F344</f>
+        <v/>
+      </c>
+      <c r="H344" s="35">
+        <f>IF(E344&gt;0, F344/E344, 0)</f>
+        <v/>
+      </c>
+      <c r="I344" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="345" ht="20" customHeight="1">
+      <c r="A345" s="10" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B345" s="32" t="n">
+        <v>3698</v>
+      </c>
+      <c r="C345" s="12" t="inlineStr">
+        <is>
+          <t>MAFER</t>
+        </is>
+      </c>
+      <c r="D345" s="12" t="inlineStr">
+        <is>
+          <t>VINO</t>
+        </is>
+      </c>
+      <c r="E345" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F345" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G345" s="13">
+        <f>E345-F345</f>
+        <v/>
+      </c>
+      <c r="H345" s="21">
+        <f>IF(E345&gt;0, F345/E345, 0)</f>
+        <v/>
+      </c>
+      <c r="I345" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="20" customHeight="1">
+      <c r="A346" s="16" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B346" s="34" t="n">
+        <v>3699</v>
+      </c>
+      <c r="C346" s="18" t="inlineStr">
+        <is>
+          <t>MAFER</t>
+        </is>
+      </c>
+      <c r="D346" s="18" t="inlineStr">
+        <is>
+          <t>VINO</t>
+        </is>
+      </c>
+      <c r="E346" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F346" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G346" s="19">
+        <f>E346-F346</f>
+        <v/>
+      </c>
+      <c r="H346" s="35">
+        <f>IF(E346&gt;0, F346/E346, 0)</f>
+        <v/>
+      </c>
+      <c r="I346" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="20" customHeight="1">
+      <c r="A347" s="10" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B347" s="32" t="n">
+        <v>3700</v>
+      </c>
+      <c r="C347" s="12" t="inlineStr">
+        <is>
+          <t>MAFER</t>
+        </is>
+      </c>
+      <c r="D347" s="12" t="inlineStr">
+        <is>
+          <t>VINO</t>
+        </is>
+      </c>
+      <c r="E347" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F347" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G347" s="13">
+        <f>E347-F347</f>
+        <v/>
+      </c>
+      <c r="H347" s="21">
+        <f>IF(E347&gt;0, F347/E347, 0)</f>
+        <v/>
+      </c>
+      <c r="I347" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" ht="20" customHeight="1">
+      <c r="A348" s="16" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B348" s="34" t="n">
+        <v>3719</v>
+      </c>
+      <c r="C348" s="18" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D348" s="18" t="inlineStr">
+        <is>
+          <t>CELESTE BB</t>
+        </is>
+      </c>
+      <c r="E348" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F348" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G348" s="19">
+        <f>E348-F348</f>
+        <v/>
+      </c>
+      <c r="H348" s="35">
+        <f>IF(E348&gt;0, F348/E348, 0)</f>
+        <v/>
+      </c>
+      <c r="I348" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="349" ht="20" customHeight="1">
+      <c r="A349" s="10" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B349" s="32" t="n">
+        <v>3720</v>
+      </c>
+      <c r="C349" s="12" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D349" s="12" t="inlineStr">
+        <is>
+          <t>CELESTE BB</t>
+        </is>
+      </c>
+      <c r="E349" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F349" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G349" s="13">
+        <f>E349-F349</f>
+        <v/>
+      </c>
+      <c r="H349" s="21">
+        <f>IF(E349&gt;0, F349/E349, 0)</f>
+        <v/>
+      </c>
+      <c r="I349" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="350" ht="20" customHeight="1">
+      <c r="A350" s="16" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B350" s="34" t="n">
+        <v>3721</v>
+      </c>
+      <c r="C350" s="18" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D350" s="18" t="inlineStr">
+        <is>
+          <t>CELESTE BB</t>
+        </is>
+      </c>
+      <c r="E350" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F350" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G350" s="19">
+        <f>E350-F350</f>
+        <v/>
+      </c>
+      <c r="H350" s="35">
+        <f>IF(E350&gt;0, F350/E350, 0)</f>
+        <v/>
+      </c>
+      <c r="I350" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="351" ht="20" customHeight="1">
+      <c r="A351" s="10" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B351" s="32" t="n">
+        <v>3722</v>
+      </c>
+      <c r="C351" s="12" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D351" s="12" t="inlineStr">
+        <is>
+          <t>CELESTE BB</t>
+        </is>
+      </c>
+      <c r="E351" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F351" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G351" s="13">
+        <f>E351-F351</f>
+        <v/>
+      </c>
+      <c r="H351" s="21">
+        <f>IF(E351&gt;0, F351/E351, 0)</f>
+        <v/>
+      </c>
+      <c r="I351" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="352" ht="20" customHeight="1">
+      <c r="A352" s="16" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B352" s="34" t="n">
+        <v>3727</v>
+      </c>
+      <c r="C352" s="18" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D352" s="18" t="inlineStr">
+        <is>
+          <t>LILA</t>
+        </is>
+      </c>
+      <c r="E352" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F352" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G352" s="19">
+        <f>E352-F352</f>
+        <v/>
+      </c>
+      <c r="H352" s="35">
+        <f>IF(E352&gt;0, F352/E352, 0)</f>
+        <v/>
+      </c>
+      <c r="I352" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="353" ht="20" customHeight="1">
+      <c r="A353" s="10" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B353" s="32" t="n">
+        <v>3728</v>
+      </c>
+      <c r="C353" s="12" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D353" s="12" t="inlineStr">
+        <is>
+          <t>LILA</t>
+        </is>
+      </c>
+      <c r="E353" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F353" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G353" s="13">
+        <f>E353-F353</f>
+        <v/>
+      </c>
+      <c r="H353" s="21">
+        <f>IF(E353&gt;0, F353/E353, 0)</f>
+        <v/>
+      </c>
+      <c r="I353" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="354" ht="20" customHeight="1">
+      <c r="A354" s="16" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B354" s="34" t="n">
+        <v>3729</v>
+      </c>
+      <c r="C354" s="18" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D354" s="18" t="inlineStr">
+        <is>
+          <t>LILA</t>
+        </is>
+      </c>
+      <c r="E354" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F354" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G354" s="19">
+        <f>E354-F354</f>
+        <v/>
+      </c>
+      <c r="H354" s="35">
+        <f>IF(E354&gt;0, F354/E354, 0)</f>
+        <v/>
+      </c>
+      <c r="I354" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="355" ht="20" customHeight="1">
+      <c r="A355" s="10" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B355" s="32" t="n">
+        <v>3730</v>
+      </c>
+      <c r="C355" s="12" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D355" s="12" t="inlineStr">
+        <is>
+          <t>LILA</t>
+        </is>
+      </c>
+      <c r="E355" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F355" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G355" s="13">
+        <f>E355-F355</f>
+        <v/>
+      </c>
+      <c r="H355" s="21">
+        <f>IF(E355&gt;0, F355/E355, 0)</f>
+        <v/>
+      </c>
+      <c r="I355" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="356" ht="20" customHeight="1">
+      <c r="A356" s="16" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B356" s="34" t="n">
+        <v>3715</v>
+      </c>
+      <c r="C356" s="18" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D356" s="18" t="inlineStr">
+        <is>
+          <t>MANTEQUILLA</t>
+        </is>
+      </c>
+      <c r="E356" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F356" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G356" s="19">
+        <f>E356-F356</f>
+        <v/>
+      </c>
+      <c r="H356" s="35">
+        <f>IF(E356&gt;0, F356/E356, 0)</f>
+        <v/>
+      </c>
+      <c r="I356" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="357" ht="20" customHeight="1">
+      <c r="A357" s="10" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B357" s="32" t="n">
+        <v>3716</v>
+      </c>
+      <c r="C357" s="12" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D357" s="12" t="inlineStr">
+        <is>
+          <t>MANTEQUILLA</t>
+        </is>
+      </c>
+      <c r="E357" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F357" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G357" s="13">
+        <f>E357-F357</f>
+        <v/>
+      </c>
+      <c r="H357" s="21">
+        <f>IF(E357&gt;0, F357/E357, 0)</f>
+        <v/>
+      </c>
+      <c r="I357" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="358" ht="20" customHeight="1">
+      <c r="A358" s="16" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B358" s="34" t="n">
+        <v>3717</v>
+      </c>
+      <c r="C358" s="18" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D358" s="18" t="inlineStr">
+        <is>
+          <t>MANTEQUILLA</t>
+        </is>
+      </c>
+      <c r="E358" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F358" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G358" s="19">
+        <f>E358-F358</f>
+        <v/>
+      </c>
+      <c r="H358" s="35">
+        <f>IF(E358&gt;0, F358/E358, 0)</f>
+        <v/>
+      </c>
+      <c r="I358" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="359" ht="20" customHeight="1">
+      <c r="A359" s="10" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B359" s="32" t="n">
+        <v>3718</v>
+      </c>
+      <c r="C359" s="12" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D359" s="12" t="inlineStr">
+        <is>
+          <t>MANTEQUILLA</t>
+        </is>
+      </c>
+      <c r="E359" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F359" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G359" s="13">
+        <f>E359-F359</f>
+        <v/>
+      </c>
+      <c r="H359" s="21">
+        <f>IF(E359&gt;0, F359/E359, 0)</f>
+        <v/>
+      </c>
+      <c r="I359" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="360" ht="20" customHeight="1">
+      <c r="A360" s="16" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B360" s="34" t="n">
+        <v>3723</v>
+      </c>
+      <c r="C360" s="18" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D360" s="18" t="inlineStr">
+        <is>
+          <t>MELON</t>
+        </is>
+      </c>
+      <c r="E360" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F360" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G360" s="19">
+        <f>E360-F360</f>
+        <v/>
+      </c>
+      <c r="H360" s="35">
+        <f>IF(E360&gt;0, F360/E360, 0)</f>
+        <v/>
+      </c>
+      <c r="I360" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="361" ht="20" customHeight="1">
+      <c r="A361" s="10" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B361" s="32" t="n">
+        <v>3724</v>
+      </c>
+      <c r="C361" s="12" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D361" s="12" t="inlineStr">
+        <is>
+          <t>MELON</t>
+        </is>
+      </c>
+      <c r="E361" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F361" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G361" s="13">
+        <f>E361-F361</f>
+        <v/>
+      </c>
+      <c r="H361" s="21">
+        <f>IF(E361&gt;0, F361/E361, 0)</f>
+        <v/>
+      </c>
+      <c r="I361" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="362" ht="20" customHeight="1">
+      <c r="A362" s="16" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B362" s="34" t="n">
+        <v>3725</v>
+      </c>
+      <c r="C362" s="18" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D362" s="18" t="inlineStr">
+        <is>
+          <t>MELON</t>
+        </is>
+      </c>
+      <c r="E362" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F362" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G362" s="19">
+        <f>E362-F362</f>
+        <v/>
+      </c>
+      <c r="H362" s="35">
+        <f>IF(E362&gt;0, F362/E362, 0)</f>
+        <v/>
+      </c>
+      <c r="I362" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="363" ht="20" customHeight="1">
+      <c r="A363" s="10" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B363" s="32" t="n">
+        <v>3726</v>
+      </c>
+      <c r="C363" s="12" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D363" s="12" t="inlineStr">
+        <is>
+          <t>MELON</t>
+        </is>
+      </c>
+      <c r="E363" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F363" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G363" s="13">
+        <f>E363-F363</f>
+        <v/>
+      </c>
+      <c r="H363" s="21">
+        <f>IF(E363&gt;0, F363/E363, 0)</f>
+        <v/>
+      </c>
+      <c r="I363" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="364" ht="20" customHeight="1">
+      <c r="A364" s="16" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B364" s="34" t="n">
+        <v>3711</v>
+      </c>
+      <c r="C364" s="18" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D364" s="18" t="inlineStr">
+        <is>
+          <t>ROSA</t>
+        </is>
+      </c>
+      <c r="E364" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F364" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G364" s="19">
+        <f>E364-F364</f>
+        <v/>
+      </c>
+      <c r="H364" s="35">
+        <f>IF(E364&gt;0, F364/E364, 0)</f>
+        <v/>
+      </c>
+      <c r="I364" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="365" ht="20" customHeight="1">
+      <c r="A365" s="10" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B365" s="32" t="n">
+        <v>3712</v>
+      </c>
+      <c r="C365" s="12" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D365" s="12" t="inlineStr">
+        <is>
+          <t>ROSA</t>
+        </is>
+      </c>
+      <c r="E365" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F365" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G365" s="13">
+        <f>E365-F365</f>
+        <v/>
+      </c>
+      <c r="H365" s="21">
+        <f>IF(E365&gt;0, F365/E365, 0)</f>
+        <v/>
+      </c>
+      <c r="I365" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="366" ht="20" customHeight="1">
+      <c r="A366" s="16" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B366" s="34" t="n">
+        <v>3713</v>
+      </c>
+      <c r="C366" s="18" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D366" s="18" t="inlineStr">
+        <is>
+          <t>ROSA</t>
+        </is>
+      </c>
+      <c r="E366" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F366" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G366" s="19">
+        <f>E366-F366</f>
+        <v/>
+      </c>
+      <c r="H366" s="35">
+        <f>IF(E366&gt;0, F366/E366, 0)</f>
+        <v/>
+      </c>
+      <c r="I366" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="367" ht="20" customHeight="1">
+      <c r="A367" s="10" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B367" s="32" t="n">
+        <v>3714</v>
+      </c>
+      <c r="C367" s="12" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D367" s="12" t="inlineStr">
+        <is>
+          <t>ROSA</t>
+        </is>
+      </c>
+      <c r="E367" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F367" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G367" s="13">
+        <f>E367-F367</f>
+        <v/>
+      </c>
+      <c r="H367" s="21">
+        <f>IF(E367&gt;0, F367/E367, 0)</f>
+        <v/>
+      </c>
+      <c r="I367" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="368" ht="20" customHeight="1">
+      <c r="A368" s="16" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B368" s="34" t="n">
+        <v>3701</v>
+      </c>
+      <c r="C368" s="18" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D368" s="18" t="inlineStr">
+        <is>
+          <t>VINO</t>
+        </is>
+      </c>
+      <c r="E368" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F368" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G368" s="19">
+        <f>E368-F368</f>
+        <v/>
+      </c>
+      <c r="H368" s="35">
+        <f>IF(E368&gt;0, F368/E368, 0)</f>
+        <v/>
+      </c>
+      <c r="I368" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="369" ht="20" customHeight="1">
+      <c r="A369" s="10" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B369" s="32" t="n">
+        <v>3702</v>
+      </c>
+      <c r="C369" s="12" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D369" s="12" t="inlineStr">
+        <is>
+          <t>VINO</t>
+        </is>
+      </c>
+      <c r="E369" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F369" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G369" s="13">
+        <f>E369-F369</f>
+        <v/>
+      </c>
+      <c r="H369" s="21">
+        <f>IF(E369&gt;0, F369/E369, 0)</f>
+        <v/>
+      </c>
+      <c r="I369" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="370" ht="20" customHeight="1">
+      <c r="A370" s="16" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B370" s="34" t="n">
+        <v>3703</v>
+      </c>
+      <c r="C370" s="18" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D370" s="18" t="inlineStr">
+        <is>
+          <t>VINO</t>
+        </is>
+      </c>
+      <c r="E370" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F370" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G370" s="19">
+        <f>E370-F370</f>
+        <v/>
+      </c>
+      <c r="H370" s="35">
+        <f>IF(E370&gt;0, F370/E370, 0)</f>
+        <v/>
+      </c>
+      <c r="I370" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="371" ht="20" customHeight="1">
+      <c r="A371" s="10" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B371" s="32" t="n">
+        <v>3704</v>
+      </c>
+      <c r="C371" s="12" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D371" s="12" t="inlineStr">
+        <is>
+          <t>VINO</t>
+        </is>
+      </c>
+      <c r="E371" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F371" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G371" s="13">
+        <f>E371-F371</f>
+        <v/>
+      </c>
+      <c r="H371" s="21">
+        <f>IF(E371&gt;0, F371/E371, 0)</f>
+        <v/>
+      </c>
+      <c r="I371" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="372" ht="20" customHeight="1">
+      <c r="A372" s="16" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B372" s="34" t="n">
+        <v>3705</v>
+      </c>
+      <c r="C372" s="18" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D372" s="18" t="inlineStr">
+        <is>
+          <t>VINO</t>
+        </is>
+      </c>
+      <c r="E372" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F372" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G372" s="19">
+        <f>E372-F372</f>
+        <v/>
+      </c>
+      <c r="H372" s="35">
+        <f>IF(E372&gt;0, F372/E372, 0)</f>
+        <v/>
+      </c>
+      <c r="I372" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="373" ht="20" customHeight="1">
+      <c r="A373" s="10" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B373" s="32" t="n">
+        <v>3706</v>
+      </c>
+      <c r="C373" s="12" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D373" s="12" t="inlineStr">
+        <is>
+          <t>VINO</t>
+        </is>
+      </c>
+      <c r="E373" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F373" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G373" s="13">
+        <f>E373-F373</f>
+        <v/>
+      </c>
+      <c r="H373" s="21">
+        <f>IF(E373&gt;0, F373/E373, 0)</f>
+        <v/>
+      </c>
+      <c r="I373" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="374" ht="20" customHeight="1">
+      <c r="A374" s="16" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B374" s="34" t="n">
+        <v>3707</v>
+      </c>
+      <c r="C374" s="18" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D374" s="18" t="inlineStr">
+        <is>
+          <t>VINO</t>
+        </is>
+      </c>
+      <c r="E374" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F374" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G374" s="19">
+        <f>E374-F374</f>
+        <v/>
+      </c>
+      <c r="H374" s="35">
+        <f>IF(E374&gt;0, F374/E374, 0)</f>
+        <v/>
+      </c>
+      <c r="I374" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="375" ht="20" customHeight="1">
+      <c r="A375" s="10" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B375" s="32" t="n">
+        <v>3708</v>
+      </c>
+      <c r="C375" s="12" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D375" s="12" t="inlineStr">
+        <is>
+          <t>VINO</t>
+        </is>
+      </c>
+      <c r="E375" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F375" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G375" s="13">
+        <f>E375-F375</f>
+        <v/>
+      </c>
+      <c r="H375" s="21">
+        <f>IF(E375&gt;0, F375/E375, 0)</f>
+        <v/>
+      </c>
+      <c r="I375" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="376" ht="20" customHeight="1">
+      <c r="A376" s="16" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B376" s="34" t="n">
+        <v>3709</v>
+      </c>
+      <c r="C376" s="18" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D376" s="18" t="inlineStr">
+        <is>
+          <t>VINO</t>
+        </is>
+      </c>
+      <c r="E376" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F376" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G376" s="19">
+        <f>E376-F376</f>
+        <v/>
+      </c>
+      <c r="H376" s="35">
+        <f>IF(E376&gt;0, F376/E376, 0)</f>
+        <v/>
+      </c>
+      <c r="I376" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="377" ht="20" customHeight="1">
+      <c r="A377" s="10" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B377" s="32" t="n">
+        <v>3710</v>
+      </c>
+      <c r="C377" s="12" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D377" s="12" t="inlineStr">
+        <is>
+          <t>VINO</t>
+        </is>
+      </c>
+      <c r="E377" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F377" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G377" s="13">
+        <f>E377-F377</f>
+        <v/>
+      </c>
+      <c r="H377" s="21">
+        <f>IF(E377&gt;0, F377/E377, 0)</f>
+        <v/>
+      </c>
+      <c r="I377" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="378" ht="20" customHeight="1">
+      <c r="A378" s="16" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="B378" s="34" t="n">
+        <v>3748</v>
+      </c>
+      <c r="C378" s="18" t="inlineStr">
+        <is>
+          <t>CARLOTA</t>
+        </is>
+      </c>
+      <c r="D378" s="18" t="inlineStr">
+        <is>
+          <t>LEOPARDO</t>
+        </is>
+      </c>
+      <c r="E378" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F378" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G378" s="19">
+        <f>E378-F378</f>
+        <v/>
+      </c>
+      <c r="H378" s="35">
+        <f>IF(E378&gt;0, F378/E378, 0)</f>
+        <v/>
+      </c>
+      <c r="I378" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="379" ht="20" customHeight="1">
+      <c r="A379" s="10" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="B379" s="32" t="n">
+        <v>3749</v>
+      </c>
+      <c r="C379" s="12" t="inlineStr">
+        <is>
+          <t>CRISTINA</t>
+        </is>
+      </c>
+      <c r="D379" s="12" t="inlineStr">
+        <is>
+          <t>PLATA QUEMADA</t>
+        </is>
+      </c>
+      <c r="E379" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F379" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G379" s="13">
+        <f>E379-F379</f>
+        <v/>
+      </c>
+      <c r="H379" s="21">
+        <f>IF(E379&gt;0, F379/E379, 0)</f>
+        <v/>
+      </c>
+      <c r="I379" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="380" ht="20" customHeight="1">
+      <c r="A380" s="16" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="B380" s="34" t="n">
+        <v>3745</v>
+      </c>
+      <c r="C380" s="18" t="inlineStr">
+        <is>
+          <t>FABIANA</t>
+        </is>
+      </c>
+      <c r="D380" s="18" t="inlineStr">
+        <is>
+          <t>MORO</t>
+        </is>
+      </c>
+      <c r="E380" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F380" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G380" s="19">
+        <f>E380-F380</f>
+        <v/>
+      </c>
+      <c r="H380" s="35">
+        <f>IF(E380&gt;0, F380/E380, 0)</f>
+        <v/>
+      </c>
+      <c r="I380" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="381" ht="20" customHeight="1">
+      <c r="A381" s="10" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="B381" s="32" t="n">
+        <v>3743</v>
+      </c>
+      <c r="C381" s="12" t="inlineStr">
+        <is>
+          <t>GRETA</t>
+        </is>
+      </c>
+      <c r="D381" s="12" t="inlineStr">
+        <is>
+          <t>MARRON</t>
+        </is>
+      </c>
+      <c r="E381" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F381" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G381" s="13">
+        <f>E381-F381</f>
+        <v/>
+      </c>
+      <c r="H381" s="21">
+        <f>IF(E381&gt;0, F381/E381, 0)</f>
+        <v/>
+      </c>
+      <c r="I381" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="382" ht="20" customHeight="1">
+      <c r="A382" s="16" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="B382" s="34" t="n">
+        <v>3744</v>
+      </c>
+      <c r="C382" s="18" t="inlineStr">
+        <is>
+          <t>GRETA</t>
+        </is>
+      </c>
+      <c r="D382" s="18" t="inlineStr">
+        <is>
+          <t>VINO</t>
+        </is>
+      </c>
+      <c r="E382" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F382" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G382" s="19">
+        <f>E382-F382</f>
+        <v/>
+      </c>
+      <c r="H382" s="35">
+        <f>IF(E382&gt;0, F382/E382, 0)</f>
+        <v/>
+      </c>
+      <c r="I382" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="383" ht="20" customHeight="1">
+      <c r="A383" s="10" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="B383" s="32" t="n">
+        <v>3747</v>
+      </c>
+      <c r="C383" s="12" t="inlineStr">
+        <is>
+          <t>MAFER</t>
+        </is>
+      </c>
+      <c r="D383" s="12" t="inlineStr">
+        <is>
+          <t>MARRON</t>
+        </is>
+      </c>
+      <c r="E383" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F383" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G383" s="13">
+        <f>E383-F383</f>
+        <v/>
+      </c>
+      <c r="H383" s="21">
+        <f>IF(E383&gt;0, F383/E383, 0)</f>
+        <v/>
+      </c>
+      <c r="I383" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="384" ht="20" customHeight="1">
+      <c r="A384" s="16" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="B384" s="34" t="n">
+        <v>3746</v>
+      </c>
+      <c r="C384" s="18" t="inlineStr">
+        <is>
+          <t>MAFER</t>
+        </is>
+      </c>
+      <c r="D384" s="18" t="inlineStr">
+        <is>
+          <t>VINO</t>
+        </is>
+      </c>
+      <c r="E384" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F384" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G384" s="19">
+        <f>E384-F384</f>
+        <v/>
+      </c>
+      <c r="H384" s="35">
+        <f>IF(E384&gt;0, F384/E384, 0)</f>
+        <v/>
+      </c>
+      <c r="I384" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="385" ht="20" customHeight="1">
+      <c r="A385" s="10" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="B385" s="32" t="n">
+        <v>3741</v>
+      </c>
+      <c r="C385" s="12" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D385" s="12" t="inlineStr">
+        <is>
+          <t>CELESTE BB</t>
+        </is>
+      </c>
+      <c r="E385" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F385" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G385" s="13">
+        <f>E385-F385</f>
+        <v/>
+      </c>
+      <c r="H385" s="21">
+        <f>IF(E385&gt;0, F385/E385, 0)</f>
+        <v/>
+      </c>
+      <c r="I385" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="386" ht="20" customHeight="1">
+      <c r="A386" s="16" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="B386" s="34" t="n">
+        <v>3737</v>
+      </c>
+      <c r="C386" s="18" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D386" s="18" t="inlineStr">
+        <is>
+          <t>LILA</t>
+        </is>
+      </c>
+      <c r="E386" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F386" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G386" s="19">
+        <f>E386-F386</f>
+        <v/>
+      </c>
+      <c r="H386" s="35">
+        <f>IF(E386&gt;0, F386/E386, 0)</f>
+        <v/>
+      </c>
+      <c r="I386" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="387" ht="20" customHeight="1">
+      <c r="A387" s="10" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="B387" s="32" t="n">
+        <v>3742</v>
+      </c>
+      <c r="C387" s="12" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D387" s="12" t="inlineStr">
+        <is>
+          <t>MANTEQUILLA</t>
+        </is>
+      </c>
+      <c r="E387" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F387" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G387" s="13">
+        <f>E387-F387</f>
+        <v/>
+      </c>
+      <c r="H387" s="21">
+        <f>IF(E387&gt;0, F387/E387, 0)</f>
+        <v/>
+      </c>
+      <c r="I387" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="388" ht="20" customHeight="1">
+      <c r="A388" s="16" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="B388" s="34" t="n">
+        <v>3739</v>
+      </c>
+      <c r="C388" s="18" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D388" s="18" t="inlineStr">
+        <is>
+          <t>MELON</t>
+        </is>
+      </c>
+      <c r="E388" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F388" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G388" s="19">
+        <f>E388-F388</f>
+        <v/>
+      </c>
+      <c r="H388" s="35">
+        <f>IF(E388&gt;0, F388/E388, 0)</f>
+        <v/>
+      </c>
+      <c r="I388" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="389" ht="20" customHeight="1">
+      <c r="A389" s="10" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="B389" s="32" t="n">
+        <v>3740</v>
+      </c>
+      <c r="C389" s="12" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D389" s="12" t="inlineStr">
+        <is>
+          <t>ROSA</t>
+        </is>
+      </c>
+      <c r="E389" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F389" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G389" s="13">
+        <f>E389-F389</f>
+        <v/>
+      </c>
+      <c r="H389" s="21">
+        <f>IF(E389&gt;0, F389/E389, 0)</f>
+        <v/>
+      </c>
+      <c r="I389" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="390" ht="20" customHeight="1">
+      <c r="A390" s="16" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="B390" s="34" t="n">
+        <v>3738</v>
+      </c>
+      <c r="C390" s="18" t="inlineStr">
+        <is>
+          <t>MICAELA</t>
+        </is>
+      </c>
+      <c r="D390" s="18" t="inlineStr">
+        <is>
+          <t>VINO</t>
+        </is>
+      </c>
+      <c r="E390" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F390" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G390" s="19">
+        <f>E390-F390</f>
+        <v/>
+      </c>
+      <c r="H390" s="35">
+        <f>IF(E390&gt;0, F390/E390, 0)</f>
+        <v/>
+      </c>
+      <c r="I390" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="391" ht="20" customHeight="1">
+      <c r="A391" s="10" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B391" s="32" t="n">
+        <v>3750</v>
+      </c>
+      <c r="C391" s="12" t="inlineStr">
+        <is>
+          <t>DEMI</t>
+        </is>
+      </c>
+      <c r="D391" s="12" t="inlineStr">
+        <is>
+          <t>NEGRO</t>
+        </is>
+      </c>
+      <c r="E391" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F391" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G391" s="13">
+        <f>E391-F391</f>
+        <v/>
+      </c>
+      <c r="H391" s="21">
+        <f>IF(E391&gt;0, F391/E391, 0)</f>
+        <v/>
+      </c>
+      <c r="I391" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="392" ht="20" customHeight="1">
+      <c r="A392" s="16" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B392" s="34" t="n">
+        <v>3751</v>
+      </c>
+      <c r="C392" s="18" t="inlineStr">
+        <is>
+          <t>DEMI</t>
+        </is>
+      </c>
+      <c r="D392" s="18" t="inlineStr">
+        <is>
+          <t>NEGRO</t>
+        </is>
+      </c>
+      <c r="E392" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F392" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G392" s="19">
+        <f>E392-F392</f>
+        <v/>
+      </c>
+      <c r="H392" s="35">
+        <f>IF(E392&gt;0, F392/E392, 0)</f>
+        <v/>
+      </c>
+      <c r="I392" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="393" ht="20" customHeight="1">
+      <c r="A393" s="10" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B393" s="32" t="n">
+        <v>3752</v>
+      </c>
+      <c r="C393" s="12" t="inlineStr">
+        <is>
+          <t>DEMI</t>
+        </is>
+      </c>
+      <c r="D393" s="12" t="inlineStr">
+        <is>
+          <t>NEGRO</t>
+        </is>
+      </c>
+      <c r="E393" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F393" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G393" s="13">
+        <f>E393-F393</f>
+        <v/>
+      </c>
+      <c r="H393" s="21">
+        <f>IF(E393&gt;0, F393/E393, 0)</f>
+        <v/>
+      </c>
+      <c r="I393" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="394" ht="20" customHeight="1">
+      <c r="A394" s="16" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B394" s="34" t="n">
+        <v>3753</v>
+      </c>
+      <c r="C394" s="18" t="inlineStr">
+        <is>
+          <t>DEMI</t>
+        </is>
+      </c>
+      <c r="D394" s="18" t="inlineStr">
+        <is>
+          <t>NEGRO</t>
+        </is>
+      </c>
+      <c r="E394" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F394" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G394" s="19">
+        <f>E394-F394</f>
+        <v/>
+      </c>
+      <c r="H394" s="35">
+        <f>IF(E394&gt;0, F394/E394, 0)</f>
+        <v/>
+      </c>
+      <c r="I394" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="395" ht="20" customHeight="1">
+      <c r="A395" s="10" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B395" s="32" t="n">
+        <v>3754</v>
+      </c>
+      <c r="C395" s="12" t="inlineStr">
+        <is>
+          <t>DEMI</t>
+        </is>
+      </c>
+      <c r="D395" s="12" t="inlineStr">
+        <is>
+          <t>NEGRO</t>
+        </is>
+      </c>
+      <c r="E395" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F395" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G395" s="13">
+        <f>E395-F395</f>
+        <v/>
+      </c>
+      <c r="H395" s="21">
+        <f>IF(E395&gt;0, F395/E395, 0)</f>
+        <v/>
+      </c>
+      <c r="I395" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="396" ht="20" customHeight="1">
+      <c r="A396" s="16" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B396" s="34" t="n">
+        <v>3755</v>
+      </c>
+      <c r="C396" s="18" t="inlineStr">
+        <is>
+          <t>DEMI</t>
+        </is>
+      </c>
+      <c r="D396" s="18" t="inlineStr">
+        <is>
+          <t>NEGRO</t>
+        </is>
+      </c>
+      <c r="E396" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F396" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G396" s="19">
+        <f>E396-F396</f>
+        <v/>
+      </c>
+      <c r="H396" s="35">
+        <f>IF(E396&gt;0, F396/E396, 0)</f>
+        <v/>
+      </c>
+      <c r="I396" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="397" ht="24" customHeight="1">
+      <c r="A397" s="24" t="inlineStr">
         <is>
           <t>TOTAL GENERAL</t>
         </is>
       </c>
-      <c r="B342" s="25" t="inlineStr"/>
-      <c r="C342" s="25" t="inlineStr"/>
-      <c r="D342" s="25" t="inlineStr"/>
-      <c r="E342" s="26">
-        <f>SUM(E5:E341)</f>
-        <v/>
-      </c>
-      <c r="F342" s="26">
-        <f>SUM(F5:F341)</f>
-        <v/>
-      </c>
-      <c r="G342" s="27">
-        <f>E342-F342</f>
-        <v/>
-      </c>
-      <c r="H342" s="28">
-        <f>IF(E342&gt;0, F342/E342, 0)</f>
-        <v/>
-      </c>
-      <c r="I342" s="25" t="inlineStr"/>
+      <c r="B397" s="25" t="inlineStr"/>
+      <c r="C397" s="25" t="inlineStr"/>
+      <c r="D397" s="25" t="inlineStr"/>
+      <c r="E397" s="26">
+        <f>SUM(E5:E396)</f>
+        <v/>
+      </c>
+      <c r="F397" s="26">
+        <f>SUM(F5:F396)</f>
+        <v/>
+      </c>
+      <c r="G397" s="27">
+        <f>E397-F397</f>
+        <v/>
+      </c>
+      <c r="H397" s="28">
+        <f>IF(E397&gt;0, F397/E397, 0)</f>
+        <v/>
+      </c>
+      <c r="I397" s="25" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -16373,7 +19169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -16427,20 +19223,20 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>MAFER</t>
+          <t>MICAELA</t>
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>408</v>
+        <v>648</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>270</v>
+        <v>145</v>
       </c>
       <c r="D5" s="13">
         <f>B5-C5</f>
         <v/>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="21">
         <f>IF(B5&gt;0, C5/B5, 0)</f>
         <v/>
       </c>
@@ -16448,20 +19244,20 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="17" t="inlineStr">
         <is>
-          <t>ZOE</t>
+          <t>MAFER</t>
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>371</v>
+        <v>504</v>
       </c>
       <c r="C6" s="20" t="n">
-        <v>250</v>
+        <v>313</v>
       </c>
       <c r="D6" s="19">
         <f>B6-C6</f>
         <v/>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="21">
         <f>IF(B6&gt;0, C6/B6, 0)</f>
         <v/>
       </c>
@@ -16469,20 +19265,20 @@
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>FABIANA</t>
+          <t>ZOE</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>240</v>
+        <v>371</v>
       </c>
       <c r="C7" s="14" t="n">
-        <v>122</v>
+        <v>298</v>
       </c>
       <c r="D7" s="13">
         <f>B7-C7</f>
         <v/>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="21">
         <f>IF(B7&gt;0, C7/B7, 0)</f>
         <v/>
       </c>
@@ -16490,20 +19286,20 @@
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>REBECA</t>
+          <t>FABIANA</t>
         </is>
       </c>
       <c r="B8" s="19" t="n">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="C8" s="20" t="n">
-        <v>226</v>
+        <v>165</v>
       </c>
       <c r="D8" s="19">
         <f>B8-C8</f>
         <v/>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="21">
         <f>IF(B8&gt;0, C8/B8, 0)</f>
         <v/>
       </c>
@@ -16511,20 +19307,20 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>MICAELA</t>
+          <t>REBECA</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="C9" s="14" t="n">
-        <v>75</v>
+        <v>232</v>
       </c>
       <c r="D9" s="13">
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="21">
         <f>IF(B9&gt;0, C9/B9, 0)</f>
         <v/>
       </c>
@@ -16532,20 +19328,20 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>ABRIL</t>
+          <t>GRETA</t>
         </is>
       </c>
       <c r="B10" s="19" t="n">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="C10" s="20" t="n">
-        <v>53</v>
+        <v>139</v>
       </c>
       <c r="D10" s="19">
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="21">
         <f>IF(B10&gt;0, C10/B10, 0)</f>
         <v/>
       </c>
@@ -16553,20 +19349,20 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>ANTONELLA</t>
+          <t>ABRIL</t>
         </is>
       </c>
       <c r="B11" s="13" t="n">
         <v>180</v>
       </c>
       <c r="C11" s="14" t="n">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="D11" s="13">
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="21">
         <f>IF(B11&gt;0, C11/B11, 0)</f>
         <v/>
       </c>
@@ -16574,20 +19370,20 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>CANDELA</t>
+          <t>ANTONELLA</t>
         </is>
       </c>
       <c r="B12" s="19" t="n">
         <v>180</v>
       </c>
       <c r="C12" s="20" t="n">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="D12" s="19">
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="21">
         <f>IF(B12&gt;0, C12/B12, 0)</f>
         <v/>
       </c>
@@ -16595,20 +19391,20 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>FLAVIA</t>
+          <t>CANDELA</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
         <v>180</v>
       </c>
-      <c r="C13" s="21" t="n">
-        <v>0</v>
+      <c r="C13" s="14" t="n">
+        <v>169</v>
       </c>
       <c r="D13" s="13">
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="21">
         <f>IF(B13&gt;0, C13/B13, 0)</f>
         <v/>
       </c>
@@ -16616,20 +19412,20 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="17" t="inlineStr">
         <is>
-          <t>GRETA</t>
+          <t>CARLOTA</t>
         </is>
       </c>
       <c r="B14" s="19" t="n">
         <v>180</v>
       </c>
       <c r="C14" s="20" t="n">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="D14" s="19">
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="21">
         <f>IF(B14&gt;0, C14/B14, 0)</f>
         <v/>
       </c>
@@ -16637,20 +19433,20 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>INES</t>
+          <t>FLAVIA</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
         <v>180</v>
       </c>
-      <c r="C15" s="14" t="n">
-        <v>121</v>
+      <c r="C15" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="D15" s="13">
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="21">
         <f>IF(B15&gt;0, C15/B15, 0)</f>
         <v/>
       </c>
@@ -16658,7 +19454,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="17" t="inlineStr">
         <is>
-          <t>LORENA</t>
+          <t>GRISSEL</t>
         </is>
       </c>
       <c r="B16" s="19" t="n">
@@ -16671,7 +19467,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="21">
         <f>IF(B16&gt;0, C16/B16, 0)</f>
         <v/>
       </c>
@@ -16679,20 +19475,20 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>LUISA</t>
+          <t>INES</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
         <v>180</v>
       </c>
       <c r="C17" s="14" t="n">
-        <v>161</v>
+        <v>121</v>
       </c>
       <c r="D17" s="13">
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="21">
         <f>IF(B17&gt;0, C17/B17, 0)</f>
         <v/>
       </c>
@@ -16700,7 +19496,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="17" t="inlineStr">
         <is>
-          <t>NATALIA</t>
+          <t>LORENA</t>
         </is>
       </c>
       <c r="B18" s="19" t="n">
@@ -16713,7 +19509,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="21">
         <f>IF(B18&gt;0, C18/B18, 0)</f>
         <v/>
       </c>
@@ -16721,20 +19517,20 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>SIENNA</t>
+          <t>LUISA</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
         <v>180</v>
       </c>
       <c r="C19" s="14" t="n">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="D19" s="13">
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="21">
         <f>IF(B19&gt;0, C19/B19, 0)</f>
         <v/>
       </c>
@@ -16742,11 +19538,11 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>CARLOTA</t>
+          <t>NATALIA</t>
         </is>
       </c>
       <c r="B20" s="19" t="n">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>0</v>
@@ -16755,7 +19551,7 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="21">
         <f>IF(B20&gt;0, C20/B20, 0)</f>
         <v/>
       </c>
@@ -16763,20 +19559,20 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>GRISSEL</t>
+          <t>SIENNA</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>144</v>
-      </c>
-      <c r="C21" s="21" t="n">
-        <v>0</v>
+        <v>180</v>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>160</v>
       </c>
       <c r="D21" s="13">
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="21">
         <f>IF(B21&gt;0, C21/B21, 0)</f>
         <v/>
       </c>
@@ -16790,14 +19586,14 @@
       <c r="B22" s="19" t="n">
         <v>144</v>
       </c>
-      <c r="C22" s="23" t="n">
-        <v>0</v>
+      <c r="C22" s="20" t="n">
+        <v>94</v>
       </c>
       <c r="D22" s="19">
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="21">
         <f>IF(B22&gt;0, C22/B22, 0)</f>
         <v/>
       </c>
@@ -16805,20 +19601,20 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>ALESSIA</t>
+          <t>CRISTINA</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>120</v>
-      </c>
-      <c r="C23" s="21" t="n">
-        <v>0</v>
+        <v>126</v>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>83</v>
       </c>
       <c r="D23" s="13">
         <f>B23-C23</f>
         <v/>
       </c>
-      <c r="E23" s="15">
+      <c r="E23" s="21">
         <f>IF(B23&gt;0, C23/B23, 0)</f>
         <v/>
       </c>
@@ -16826,20 +19622,20 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>CRISTINA</t>
+          <t>ALESSIA</t>
         </is>
       </c>
       <c r="B24" s="19" t="n">
         <v>120</v>
       </c>
-      <c r="C24" s="20" t="n">
-        <v>82</v>
+      <c r="C24" s="23" t="n">
+        <v>0</v>
       </c>
       <c r="D24" s="19">
         <f>B24-C24</f>
         <v/>
       </c>
-      <c r="E24" s="15">
+      <c r="E24" s="21">
         <f>IF(B24&gt;0, C24/B24, 0)</f>
         <v/>
       </c>
@@ -16847,44 +19643,65 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>MILUSKA</t>
+          <t>DEMI</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>36</v>
-      </c>
-      <c r="C25" s="14" t="n">
-        <v>24</v>
+        <v>72</v>
+      </c>
+      <c r="C25" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="D25" s="13">
         <f>B25-C25</f>
         <v/>
       </c>
-      <c r="E25" s="15">
+      <c r="E25" s="21">
         <f>IF(B25&gt;0, C25/B25, 0)</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="37" t="inlineStr">
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>MILUSKA</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="n">
+        <v>36</v>
+      </c>
+      <c r="C26" s="20" t="n">
+        <v>32</v>
+      </c>
+      <c r="D26" s="19">
+        <f>B26-C26</f>
+        <v/>
+      </c>
+      <c r="E26" s="21">
+        <f>IF(B26&gt;0, C26/B26, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="37" t="inlineStr">
         <is>
           <t>TOTAL GENERAL</t>
         </is>
       </c>
-      <c r="B26" s="26">
-        <f>SUM(B5:B25)</f>
-        <v/>
-      </c>
-      <c r="C26" s="26">
-        <f>SUM(C5:C25)</f>
-        <v/>
-      </c>
-      <c r="D26" s="27">
-        <f>B26-C26</f>
-        <v/>
-      </c>
-      <c r="E26" s="28">
-        <f>IF(B26&gt;0, C26/B26, 0)</f>
+      <c r="B27" s="26">
+        <f>SUM(B5:B26)</f>
+        <v/>
+      </c>
+      <c r="C27" s="26">
+        <f>SUM(C5:C26)</f>
+        <v/>
+      </c>
+      <c r="D27" s="27">
+        <f>B27-C27</f>
+        <v/>
+      </c>
+      <c r="E27" s="28">
+        <f>IF(B27&gt;0, C27/B27, 0)</f>
         <v/>
       </c>
     </row>
